--- a/literature/PAPERS_TABLE_v2.xlsx
+++ b/literature/PAPERS_TABLE_v2.xlsx
@@ -950,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
@@ -1397,6 +1397,15 @@
     <xf numFmtId="0" fontId="71" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="38" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1409,14 +1418,8 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="38" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -7590,3177 +7593,2847 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:G86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="49" min="1" max="1"/>
-    <col width="40.08984375" customWidth="1" style="49" min="2" max="2"/>
-    <col width="44" customWidth="1" style="49" min="3" max="3"/>
-    <col width="46" customWidth="1" style="49" min="4" max="4"/>
-    <col width="36" customWidth="1" style="49" min="5" max="5"/>
-    <col width="14" customWidth="1" style="49" min="6" max="6"/>
-    <col width="52" customWidth="1" style="49" min="7" max="7"/>
+    <col width="24" customWidth="1" style="49" min="1" max="1"/>
+    <col width="34" customWidth="1" style="49" min="2" max="2"/>
+    <col width="22" customWidth="1" style="49" min="3" max="3"/>
+    <col width="42" customWidth="1" style="49" min="4" max="4"/>
+    <col width="7" customWidth="1" style="49" min="5" max="5"/>
+    <col width="40" customWidth="1" style="49" min="6" max="6"/>
+    <col width="30" customWidth="1" style="49" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="49">
-      <c r="A1" s="54" t="inlineStr">
-        <is>
-          <t>All tools</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" s="49">
-      <c r="A2" s="48" t="n"/>
-    </row>
-    <row r="3" ht="6" customHeight="1" s="49"/>
-    <row r="5" ht="30" customHeight="1" s="49">
-      <c r="B5" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="49">
+      <c r="A1" s="154" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="49">
+      <c r="A2" s="155" t="inlineStr">
+        <is>
+          <t>One row per tool. 'Used by' names the paper that used it. A dash means nobody in my review used it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1" s="49"/>
+    <row r="4" ht="28" customHeight="1" s="49">
+      <c r="A4" s="156" t="inlineStr">
         <is>
           <t>Tool</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>What it is, in one line</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>What it does</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="B4" s="156" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C4" s="156" t="inlineStr">
+        <is>
+          <t>Used by</t>
+        </is>
+      </c>
+      <c r="D4" s="156" t="inlineStr">
+        <is>
+          <t>How they used it</t>
+        </is>
+      </c>
+      <c r="E4" s="156" t="inlineStr">
+        <is>
+          <t>Us?</t>
+        </is>
+      </c>
+      <c r="F4" s="156" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="G4" s="156" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Do we use it?</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>Why, or why not</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" s="49">
-      <c r="B6" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE LANGUAGES</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" s="49">
-      <c r="B7" s="42" t="inlineStr">
+    </row>
+    <row r="5" ht="24" customHeight="1" s="49">
+      <c r="A5" s="157" t="inlineStr">
+        <is>
+          <t>1. Languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" s="49">
+      <c r="A6" s="158" t="inlineStr">
         <is>
           <t>RDF</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>The rule that all data is made of three-part sentences: subject, predicate, object</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Lets you add any new fact without changing a schema. 'Cetaphil contains Phenoxyethanol' is one triple</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="B6" s="159" t="inlineStr">
+        <is>
+          <t>Data written as three-part facts</t>
+        </is>
+      </c>
+      <c r="C6" s="159" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="D6" s="159" t="inlineStr">
+        <is>
+          <t>The base layer under every ontology here</t>
+        </is>
+      </c>
+      <c r="E6" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F6" s="159" t="inlineStr">
+        <is>
+          <t>What an ontology is made of</t>
+        </is>
+      </c>
+      <c r="G6" s="161" t="inlineStr">
         <is>
           <t>w3.org/TR/rdf11-primer</t>
         </is>
       </c>
-      <c r="F7" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>It is what an ontology is written in. No choice here</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" s="49">
-      <c r="B8" s="42" t="inlineStr">
+    </row>
+    <row r="7" ht="32" customHeight="1" s="49">
+      <c r="A7" s="158" t="inlineStr">
         <is>
           <t>Turtle (.ttl)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>The readable way of writing RDF</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Our ontology file. Diffs cleanly in git</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>The readable way to write RDF</t>
+        </is>
+      </c>
+      <c r="C7" s="159" t="inlineStr">
+        <is>
+          <t>Abesova, TOXIN</t>
+        </is>
+      </c>
+      <c r="D7" s="159" t="inlineStr">
+        <is>
+          <t>Abesova exported nine .ttl files and merged them</t>
+        </is>
+      </c>
+      <c r="E7" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F7" s="159" t="inlineStr">
+        <is>
+          <t>Humans can read it, and it diffs in git</t>
+        </is>
+      </c>
+      <c r="G7" s="161" t="inlineStr">
         <is>
           <t>w3.org/TR/turtle</t>
         </is>
       </c>
-      <c r="F8" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Readable by humans, which the other formats are not</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" s="49">
-      <c r="B9" s="42" t="inlineStr">
+    </row>
+    <row r="8" ht="45" customHeight="1" s="49">
+      <c r="A8" s="158" t="inlineStr">
         <is>
           <t>OWL</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>RDF plus real logic</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Lets you say 'a sensitive-safe product is any product with no allergens' and have software work out who qualifies</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="B8" s="159" t="inlineStr">
+        <is>
+          <t>RDF plus logic</t>
+        </is>
+      </c>
+      <c r="C8" s="159" t="inlineStr">
+        <is>
+          <t>Moe &amp; Aung, OntoCosmetic, Hansanie, Abesova, COPPER, DermO</t>
+        </is>
+      </c>
+      <c r="D8" s="159" t="inlineStr">
+        <is>
+          <t>Abesova defined OilySkinProducts as hasOilyScore value 5</t>
+        </is>
+      </c>
+      <c r="E8" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="159" t="inlineStr">
+        <is>
+          <t>My defined classes need it</t>
+        </is>
+      </c>
+      <c r="G8" s="161" t="inlineStr">
         <is>
           <t>w3.org/TR/owl2-primer</t>
         </is>
       </c>
-      <c r="F9" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>The defined classes need it. This is what makes it an ontology and not a spreadsheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" s="49">
-      <c r="B10" s="42" t="inlineStr">
+    </row>
+    <row r="9" ht="45" customHeight="1" s="49">
+      <c r="A9" s="158" t="inlineStr">
         <is>
           <t>SPARQL</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>The query language for graphs. SQL for RDF. Say 'sparkle'</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Answers questions like 'oily skin, no allergens, under $20, in Beirut'. Abesova, bit-Tech, TOXIN and FoodKG all use it</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="B9" s="159" t="inlineStr">
+        <is>
+          <t>The query language for graphs</t>
+        </is>
+      </c>
+      <c r="C9" s="159" t="inlineStr">
+        <is>
+          <t>Abesova, bit-Tech, Utari, FoodKG, Di Noia</t>
+        </is>
+      </c>
+      <c r="D9" s="159" t="inlineStr">
+        <is>
+          <t>Abesova ranks reviews and picks the top 3 per category</t>
+        </is>
+      </c>
+      <c r="E9" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" s="159" t="inlineStr">
+        <is>
+          <t>My 15 competency questions become 15 queries</t>
+        </is>
+      </c>
+      <c r="G9" s="161" t="inlineStr">
         <is>
           <t>w3.org/TR/sparql11-query</t>
         </is>
       </c>
-      <c r="F10" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Our 15 competency questions are each one SPARQL query</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" s="49">
-      <c r="B11" s="42" t="inlineStr">
+    </row>
+    <row r="10" ht="32" customHeight="1" s="49">
+      <c r="A10" s="158" t="inlineStr">
         <is>
           <t>SWRL</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>If-then rules for what OWL cannot say</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>OntoCosmetic writes its formulation rules in it. 'If product has a declarable allergen then not for sensitive skin'</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="B10" s="159" t="inlineStr">
+        <is>
+          <t>If-then rules on top of OWL</t>
+        </is>
+      </c>
+      <c r="C10" s="159" t="inlineStr">
+        <is>
+          <t>OntoCosmetic</t>
+        </is>
+      </c>
+      <c r="D10" s="159" t="inlineStr">
+        <is>
+          <t>Formulation rules with a high and low threshold each</t>
+        </is>
+      </c>
+      <c r="E10" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F10" s="159" t="inlineStr">
+        <is>
+          <t>Slows the reasoner. Two rules at most</t>
+        </is>
+      </c>
+      <c r="G10" s="161" t="inlineStr">
         <is>
           <t>w3.org/submissions/SWRL</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Only for two rules. It slows reasoning, and HermiT ignores it silently, so we would switch to Openllet</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" s="49">
-      <c r="B12" s="42" t="inlineStr">
+    </row>
+    <row r="11" ht="19" customHeight="1" s="49">
+      <c r="A11" s="158" t="inlineStr">
         <is>
           <t>SHACL</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Checks the data obeys rules. OWL says what follows, SHACL says what MUST be true</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>'Every product must have exactly one brand.' Our validate_dataset.py, moved onto the graph</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="B11" s="159" t="inlineStr">
+        <is>
+          <t>Checks data and can infer</t>
+        </is>
+      </c>
+      <c r="C11" s="159" t="inlineStr">
+        <is>
+          <t>nobody. 0 of 28</t>
+        </is>
+      </c>
+      <c r="D11" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F11" s="159" t="inlineStr">
+        <is>
+          <t>OWL cannot report an error. SHACL can</t>
+        </is>
+      </c>
+      <c r="G11" s="161" t="inlineStr">
         <is>
           <t>w3.org/TR/shacl</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>OWL assumes anything unsaid might be true, so it cannot enforce. SHACL can</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" s="49">
-      <c r="B13" s="42" t="inlineStr">
-        <is>
-          <t>R2RML / RML / YARRRML</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>A file that says 'this column becomes this property'. R2RML is for databases, RML adds CSV, YARRRML is RML in readable YAML</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>TOXIN used R2RML to turn Excel into a graph. This is how our CSV becomes triples</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+    </row>
+    <row r="12" ht="32" customHeight="1" s="49">
+      <c r="A12" s="158" t="inlineStr">
+        <is>
+          <t>R2RML / RML</t>
+        </is>
+      </c>
+      <c r="B12" s="159" t="inlineStr">
+        <is>
+          <t>A file saying which column becomes what</t>
+        </is>
+      </c>
+      <c r="C12" s="159" t="inlineStr">
+        <is>
+          <t>TOXIN KG</t>
+        </is>
+      </c>
+      <c r="D12" s="159" t="inlineStr">
+        <is>
+          <t>Turned toxicology spreadsheets into triples</t>
+        </is>
+      </c>
+      <c r="E12" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" s="159" t="inlineStr">
+        <is>
+          <t>The mapping file goes in my appendix</t>
+        </is>
+      </c>
+      <c r="G12" s="161" t="inlineStr">
         <is>
           <t>rml.io</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>A mapping file goes in the appendix and can be audited. A script cannot</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" s="49">
-      <c r="B14" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EDITORS AND LIBRARIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" s="49">
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>Protégé</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>The free desktop editor from Stanford. Everyone uses it</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Build classes by clicking, press the reasoner button, screenshot the hierarchy. Moe, OntoCosmetic, Hansanie and COPPER all used it</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+    </row>
+    <row r="13" ht="24" customHeight="1" s="49">
+      <c r="A13" s="157" t="inlineStr">
+        <is>
+          <t>2. How you build it. Five of my 28 papers used no Protege at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="49">
+      <c r="A14" s="158" t="inlineStr">
+        <is>
+          <t>Protege</t>
+        </is>
+      </c>
+      <c r="B14" s="159" t="inlineStr">
+        <is>
+          <t>Free desktop ontology editor, Stanford</t>
+        </is>
+      </c>
+      <c r="C14" s="159" t="inlineStr">
+        <is>
+          <t>Moe &amp; Aung, OntoCosmetic, Hansanie, DermO, COPPER</t>
+        </is>
+      </c>
+      <c r="D14" s="159" t="inlineStr">
+        <is>
+          <t>Built classes by clicking, ran the reasoner from the menu</t>
+        </is>
+      </c>
+      <c r="E14" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F14" s="159" t="inlineStr">
+        <is>
+          <t>Standard, free, reasoners built in</t>
+        </is>
+      </c>
+      <c r="G14" s="161" t="inlineStr">
         <is>
           <t>protege.stanford.edu</t>
         </is>
       </c>
-      <c r="F15" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Standard, and reasoners are built in. But keep the Turtle file in git as the real master</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" s="49">
-      <c r="B16" s="42" t="inlineStr">
+    </row>
+    <row r="15" ht="32" customHeight="1" s="49">
+      <c r="A15" s="158" t="inlineStr">
+        <is>
+          <t>OntoRefine</t>
+        </is>
+      </c>
+      <c r="B15" s="159" t="inlineStr">
+        <is>
+          <t>Point-and-click CSV to RDF, in GraphDB</t>
+        </is>
+      </c>
+      <c r="C15" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D15" s="159" t="inlineStr">
+        <is>
+          <t>Drew the mapping for the Sephora review CSV. No Protege at all</t>
+        </is>
+      </c>
+      <c r="E15" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" s="159" t="inlineStr">
+        <is>
+          <t>The mapping is stuck inside GraphDB. I cannot publish it</t>
+        </is>
+      </c>
+      <c r="G15" s="161" t="inlineStr">
+        <is>
+          <t>graphdb.ontotext.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" s="49">
+      <c r="A16" s="158" t="inlineStr">
+        <is>
+          <t>RML mapping file</t>
+        </is>
+      </c>
+      <c r="B16" s="159" t="inlineStr">
+        <is>
+          <t>No editor. The mapping defines the graph</t>
+        </is>
+      </c>
+      <c r="C16" s="159" t="inlineStr">
+        <is>
+          <t>TOXIN KG</t>
+        </is>
+      </c>
+      <c r="D16" s="159" t="inlineStr">
+        <is>
+          <t>Wrote R2RML and never opened an editor</t>
+        </is>
+      </c>
+      <c r="E16" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" s="159" t="inlineStr">
+        <is>
+          <t>This is how my pipeline works. Built by script, not clicking</t>
+        </is>
+      </c>
+      <c r="G16" s="161" t="inlineStr">
+        <is>
+          <t>rml.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" s="49">
+      <c r="A17" s="158" t="inlineStr">
+        <is>
+          <t>Apache Jena Fuseki</t>
+        </is>
+      </c>
+      <c r="B17" s="159" t="inlineStr">
+        <is>
+          <t>Triple store with a SPARQL endpoint</t>
+        </is>
+      </c>
+      <c r="C17" s="159" t="inlineStr">
+        <is>
+          <t>bit-Tech 2025</t>
+        </is>
+      </c>
+      <c r="D17" s="159" t="inlineStr">
+        <is>
+          <t>Stored and queried the graph. No editor at all</t>
+        </is>
+      </c>
+      <c r="E17" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F17" s="159" t="inlineStr">
+        <is>
+          <t>Weaker reasoning than GraphDB</t>
+        </is>
+      </c>
+      <c r="G17" s="161" t="inlineStr">
+        <is>
+          <t>jena.apache.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" s="49">
+      <c r="A18" s="158" t="inlineStr">
+        <is>
+          <t>WebProtege</t>
+        </is>
+      </c>
+      <c r="B18" s="159" t="inlineStr">
+        <is>
+          <t>Protege in a browser, two people at once</t>
+        </is>
+      </c>
+      <c r="C18" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F18" s="159" t="inlineStr">
+        <is>
+          <t>If my supervisor wants to comment in the file</t>
+        </is>
+      </c>
+      <c r="G18" s="161" t="inlineStr">
+        <is>
+          <t>webprotege.stanford.edu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" s="49">
+      <c r="A19" s="158" t="inlineStr">
+        <is>
+          <t>TopBraid Composer</t>
+        </is>
+      </c>
+      <c r="B19" s="159" t="inlineStr">
+        <is>
+          <t>Commercial editor, best SHACL support</t>
+        </is>
+      </c>
+      <c r="C19" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F19" s="159" t="inlineStr">
+        <is>
+          <t>Commercial. Written by the SHACL authors</t>
+        </is>
+      </c>
+      <c r="G19" s="161" t="inlineStr">
+        <is>
+          <t>topquadrant.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" s="49">
+      <c r="A20" s="158" t="inlineStr">
+        <is>
+          <t>VocBench 3</t>
+        </is>
+      </c>
+      <c r="B20" s="159" t="inlineStr">
+        <is>
+          <t>Web editor for thesauri and SKOS</t>
+        </is>
+      </c>
+      <c r="C20" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F20" s="159" t="inlineStr">
+        <is>
+          <t>Built for word lists, not defined classes</t>
+        </is>
+      </c>
+      <c r="G20" s="161" t="inlineStr">
+        <is>
+          <t>vocbench.uniroma2.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="49">
+      <c r="A21" s="158" t="inlineStr">
+        <is>
+          <t>ROBOT</t>
+        </is>
+      </c>
+      <c r="B21" s="159" t="inlineStr">
+        <is>
+          <t>Command-line ontology jobs</t>
+        </is>
+      </c>
+      <c r="C21" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F21" s="159" t="inlineStr">
+        <is>
+          <t>Makes the build repeatable instead of clicked</t>
+        </is>
+      </c>
+      <c r="G21" s="161" t="inlineStr">
+        <is>
+          <t>github.com/ontodev/robot</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" s="49">
+      <c r="A22" s="158" t="inlineStr">
+        <is>
+          <t>LinkML</t>
+        </is>
+      </c>
+      <c r="B22" s="159" t="inlineStr">
+        <is>
+          <t>Write YAML, get OWL and SHACL out</t>
+        </is>
+      </c>
+      <c r="C22" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F22" s="159" t="inlineStr">
+        <is>
+          <t>One source, so OWL and SHACL cannot drift apart</t>
+        </is>
+      </c>
+      <c r="G22" s="161" t="inlineStr">
+        <is>
+          <t>linkml.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" s="49">
+      <c r="A23" s="158" t="inlineStr">
+        <is>
+          <t>Chowlk</t>
+        </is>
+      </c>
+      <c r="B23" s="159" t="inlineStr">
+        <is>
+          <t>Draw a diagram, get OWL</t>
+        </is>
+      </c>
+      <c r="C23" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F23" s="159" t="inlineStr">
+        <is>
+          <t>I need diagrams anyway. Draw once</t>
+        </is>
+      </c>
+      <c r="G23" s="161" t="inlineStr">
+        <is>
+          <t>chowlk.linkeddata.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1" s="49">
+      <c r="A24" s="158" t="inlineStr">
+        <is>
+          <t>OWLGrEd</t>
+        </is>
+      </c>
+      <c r="B24" s="159" t="inlineStr">
+        <is>
+          <t>Draws an OWL file as a picture</t>
+        </is>
+      </c>
+      <c r="C24" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F24" s="159" t="inlineStr">
+        <is>
+          <t>Only to make the figure for the chapter</t>
+        </is>
+      </c>
+      <c r="G24" s="161" t="inlineStr">
+        <is>
+          <t>owlgred.lumii.lv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" s="49">
+      <c r="A25" s="158" t="inlineStr">
+        <is>
+          <t>CoModIDE</t>
+        </is>
+      </c>
+      <c r="B25" s="159" t="inlineStr">
+        <is>
+          <t>Drag-and-drop ontology modules</t>
+        </is>
+      </c>
+      <c r="C25" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F25" s="159" t="inlineStr">
+        <is>
+          <t>Same idea as Chowlk</t>
+        </is>
+      </c>
+      <c r="G25" s="161" t="inlineStr">
+        <is>
+          <t>comodide.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1" s="49">
+      <c r="A26" s="158" t="inlineStr">
         <is>
           <t>Owlready2</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>A Python library for ontologies</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Load the ontology, add facts, run a reasoner from code. Hansanie &amp; Silva used it</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="B26" s="159" t="inlineStr">
+        <is>
+          <t>Python library for ontologies</t>
+        </is>
+      </c>
+      <c r="C26" s="159" t="inlineStr">
+        <is>
+          <t>Hansanie &amp; Silva</t>
+        </is>
+      </c>
+      <c r="D26" s="159" t="inlineStr">
+        <is>
+          <t>Queried the ontology from their Python app</t>
+        </is>
+      </c>
+      <c r="E26" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F26" s="159" t="inlineStr">
+        <is>
+          <t>My pipeline is Python</t>
+        </is>
+      </c>
+      <c r="G26" s="161" t="inlineStr">
         <is>
           <t>owlready2.readthedocs.io</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Our whole pipeline is Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1" s="49">
-      <c r="B17" s="42" t="inlineStr">
+    </row>
+    <row r="27" ht="19" customHeight="1" s="49">
+      <c r="A27" s="158" t="inlineStr">
         <is>
           <t>RDFLib</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>A Python library for plain RDF and SPARQL</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Read and write triples, run queries, from Python</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="B27" s="159" t="inlineStr">
+        <is>
+          <t>Python library for RDF</t>
+        </is>
+      </c>
+      <c r="C27" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F27" s="159" t="inlineStr">
+        <is>
+          <t>Pairs with Owlready2 and pySHACL</t>
+        </is>
+      </c>
+      <c r="G27" s="161" t="inlineStr">
         <is>
           <t>rdflib.readthedocs.io</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Same reason. Pairs with Owlready2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1" s="49">
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>CoModIDE</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>A drawing tool for ontology modules, made for the MOMo method</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Draw the module, get the OWL</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>comodide.com</t>
-        </is>
-      </c>
-      <c r="F18" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Nice for the diagrams the chapter needs. Not essential</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1" s="49">
-      <c r="B19" s="42" t="inlineStr">
+    </row>
+    <row r="28" ht="24" customHeight="1" s="49">
+      <c r="A28" s="157" t="inlineStr">
+        <is>
+          <t>3. Reasoners and rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" s="49">
+      <c r="A29" s="158" t="inlineStr">
+        <is>
+          <t>RDFS entailment</t>
+        </is>
+      </c>
+      <c r="B29" s="159" t="inlineStr">
+        <is>
+          <t>Subclass and domain/range only</t>
+        </is>
+      </c>
+      <c r="C29" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D29" s="159" t="inlineStr">
+        <is>
+          <t>Free in GraphDB, always on</t>
+        </is>
+      </c>
+      <c r="E29" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F29" s="159" t="inlineStr">
+        <is>
+          <t>Cheapest reasoning. Does the hierarchy only</t>
+        </is>
+      </c>
+      <c r="G29" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/rdf-mt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="49">
+      <c r="A30" s="158" t="inlineStr">
+        <is>
+          <t>HermiT</t>
+        </is>
+      </c>
+      <c r="B30" s="159" t="inlineStr">
+        <is>
+          <t>OWL reasoner, ships with Protege</t>
+        </is>
+      </c>
+      <c r="C30" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F30" s="159" t="inlineStr">
+        <is>
+          <t>Fills my defined classes. Solid default</t>
+        </is>
+      </c>
+      <c r="G30" s="161" t="inlineStr">
+        <is>
+          <t>hermit-reasoner.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" s="49">
+      <c r="A31" s="158" t="inlineStr">
+        <is>
+          <t>Pellet / Openllet</t>
+        </is>
+      </c>
+      <c r="B31" s="159" t="inlineStr">
+        <is>
+          <t>OWL reasoner that also runs SWRL</t>
+        </is>
+      </c>
+      <c r="C31" s="159" t="inlineStr">
+        <is>
+          <t>Hansanie &amp; Silva</t>
+        </is>
+      </c>
+      <c r="D31" s="159" t="inlineStr">
+        <is>
+          <t>Checked the ontology was consistent</t>
+        </is>
+      </c>
+      <c r="E31" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F31" s="159" t="inlineStr">
+        <is>
+          <t>Only if I write SWRL rules</t>
+        </is>
+      </c>
+      <c r="G31" s="161" t="inlineStr">
+        <is>
+          <t>github.com/Galigator/openllet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1" s="49">
+      <c r="A32" s="158" t="inlineStr">
+        <is>
+          <t>ELK</t>
+        </is>
+      </c>
+      <c r="B32" s="159" t="inlineStr">
+        <is>
+          <t>Very fast reasoner, limited logic</t>
+        </is>
+      </c>
+      <c r="C32" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F32" s="159" t="inlineStr">
+        <is>
+          <t>Too limited for my defined classes</t>
+        </is>
+      </c>
+      <c r="G32" s="161" t="inlineStr">
+        <is>
+          <t>github.com/liveontologies/elk-reasoner</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1" s="49">
+      <c r="A33" s="158" t="inlineStr">
+        <is>
+          <t>OWL 2 profiles</t>
+        </is>
+      </c>
+      <c r="B33" s="159" t="inlineStr">
+        <is>
+          <t>RL, EL, QL, DL. Power against speed</t>
+        </is>
+      </c>
+      <c r="C33" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F33" s="159" t="inlineStr">
+        <is>
+          <t>I should name mine in the chapter. It is DL</t>
+        </is>
+      </c>
+      <c r="G33" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/owl2-profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1" s="49">
+      <c r="A34" s="158" t="inlineStr">
+        <is>
+          <t>SPARQL CONSTRUCT</t>
+        </is>
+      </c>
+      <c r="B34" s="159" t="inlineStr">
+        <is>
+          <t>A query that writes new triples</t>
+        </is>
+      </c>
+      <c r="C34" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D34" s="159" t="inlineStr">
+        <is>
+          <t>Built the OilyScore triples, then the reasoner used them</t>
+        </is>
+      </c>
+      <c r="E34" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F34" s="159" t="inlineStr">
+        <is>
+          <t>Simple, but the rules sit in loose files</t>
+        </is>
+      </c>
+      <c r="G34" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/sparql11-query</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="49">
+      <c r="A35" s="158" t="inlineStr">
+        <is>
+          <t>SHACL Core</t>
+        </is>
+      </c>
+      <c r="B35" s="159" t="inlineStr">
+        <is>
+          <t>Reports which product broke a rule</t>
+        </is>
+      </c>
+      <c r="C35" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F35" s="159" t="inlineStr">
+        <is>
+          <t>Validates my 12,629 rows. OWL cannot</t>
+        </is>
+      </c>
+      <c r="G35" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/shacl</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="49">
+      <c r="A36" s="158" t="inlineStr">
+        <is>
+          <t>sh:TripleRule</t>
+        </is>
+      </c>
+      <c r="B36" s="159" t="inlineStr">
+        <is>
+          <t>Adds a triple when a condition holds</t>
+        </is>
+      </c>
+      <c r="C36" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F36" s="159" t="inlineStr">
+        <is>
+          <t>Can infer any triple. OWL only infers types</t>
+        </is>
+      </c>
+      <c r="G36" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/shacl-af</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1" s="49">
+      <c r="A37" s="158" t="inlineStr">
+        <is>
+          <t>sh:SPARQLRule</t>
+        </is>
+      </c>
+      <c r="B37" s="159" t="inlineStr">
+        <is>
+          <t>A rule that counts and writes back</t>
+        </is>
+      </c>
+      <c r="C37" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F37" s="159" t="inlineStr">
+        <is>
+          <t>OWL cannot count. This is why I add SHACL</t>
+        </is>
+      </c>
+      <c r="G37" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/shacl-af</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1" s="49">
+      <c r="A38" s="158" t="inlineStr">
+        <is>
+          <t>pySHACL</t>
+        </is>
+      </c>
+      <c r="B38" s="159" t="inlineStr">
+        <is>
+          <t>SHACL validator in Python</t>
+        </is>
+      </c>
+      <c r="C38" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F38" s="159" t="inlineStr">
+        <is>
+          <t>My pipeline is Python</t>
+        </is>
+      </c>
+      <c r="G38" s="161" t="inlineStr">
+        <is>
+          <t>github.com/RDFLib/pySHACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="49">
+      <c r="A39" s="158" t="inlineStr">
+        <is>
+          <t>Apache Jena SHACL</t>
+        </is>
+      </c>
+      <c r="B39" s="159" t="inlineStr">
+        <is>
+          <t>SHACL validator in Java, the fastest</t>
+        </is>
+      </c>
+      <c r="C39" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F39" s="159" t="inlineStr">
+        <is>
+          <t>Four times faster. Only if pySHACL gets slow</t>
+        </is>
+      </c>
+      <c r="G39" s="161" t="inlineStr">
+        <is>
+          <t>jena.apache.org/documentation/shacl</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="49">
+      <c r="A40" s="157" t="inlineStr">
+        <is>
+          <t>4. Where the graph lives</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1" s="49">
+      <c r="A41" s="158" t="inlineStr">
+        <is>
+          <t>GraphDB</t>
+        </is>
+      </c>
+      <c r="B41" s="159" t="inlineStr">
+        <is>
+          <t>Triple store with reasoning built in</t>
+        </is>
+      </c>
+      <c r="C41" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D41" s="159" t="inlineStr">
+        <is>
+          <t>Held the merged graph and ran the class restrictions</t>
+        </is>
+      </c>
+      <c r="E41" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F41" s="159" t="inlineStr">
+        <is>
+          <t>Free desktop edition, SHACL built in</t>
+        </is>
+      </c>
+      <c r="G41" s="161" t="inlineStr">
+        <is>
+          <t>graphdb.ontotext.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1" s="49">
+      <c r="A42" s="158" t="inlineStr">
+        <is>
+          <t>Morph-KGC</t>
+        </is>
+      </c>
+      <c r="B42" s="159" t="inlineStr">
+        <is>
+          <t>Python engine that runs an RML file</t>
+        </is>
+      </c>
+      <c r="C42" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F42" s="159" t="inlineStr">
+        <is>
+          <t>One command turns my CSV into triples</t>
+        </is>
+      </c>
+      <c r="G42" s="161" t="inlineStr">
+        <is>
+          <t>morph-kgc.readthedocs.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1" s="49">
+      <c r="A43" s="158" t="inlineStr">
+        <is>
+          <t>Stardog / Virtuoso</t>
+        </is>
+      </c>
+      <c r="B43" s="159" t="inlineStr">
+        <is>
+          <t>Commercial triple stores</t>
+        </is>
+      </c>
+      <c r="C43" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" s="159" t="inlineStr">
+        <is>
+          <t>I do not need the scale</t>
+        </is>
+      </c>
+      <c r="G43" s="161" t="inlineStr">
+        <is>
+          <t>stardog.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="49">
+      <c r="A44" s="157" t="inlineStr">
+        <is>
+          <t>5. Vocabularies I reuse instead of inventing</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1" s="49">
+      <c r="A45" s="158" t="inlineStr">
+        <is>
+          <t>schema.org</t>
+        </is>
+      </c>
+      <c r="B45" s="159" t="inlineStr">
+        <is>
+          <t>Google's vocabulary for products</t>
+        </is>
+      </c>
+      <c r="C45" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F45" s="159" t="inlineStr">
+        <is>
+          <t>Product, Offer, price, brand. Already understood</t>
+        </is>
+      </c>
+      <c r="G45" s="161" t="inlineStr">
+        <is>
+          <t>schema.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1" s="49">
+      <c r="A46" s="158" t="inlineStr">
+        <is>
+          <t>PROV-O</t>
+        </is>
+      </c>
+      <c r="B46" s="159" t="inlineStr">
+        <is>
+          <t>W3C standard for where a fact came from</t>
+        </is>
+      </c>
+      <c r="C46" s="159" t="inlineStr">
+        <is>
+          <t>TOXIN KG (named graphs)</t>
+        </is>
+      </c>
+      <c r="D46" s="159" t="inlineStr">
+        <is>
+          <t>One graph per source, so provenance is never lost</t>
+        </is>
+      </c>
+      <c r="E46" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F46" s="159" t="inlineStr">
+        <is>
+          <t>Turns my evidence levels into a standard</t>
+        </is>
+      </c>
+      <c r="G46" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/prov-o</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1" s="49">
+      <c r="A47" s="158" t="inlineStr">
+        <is>
+          <t>SKOS</t>
+        </is>
+      </c>
+      <c r="B47" s="159" t="inlineStr">
+        <is>
+          <t>For lists of words, not classes</t>
+        </is>
+      </c>
+      <c r="C47" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F47" s="159" t="inlineStr">
+        <is>
+          <t>My benefits list is terms, not logic</t>
+        </is>
+      </c>
+      <c r="G47" s="161" t="inlineStr">
+        <is>
+          <t>w3.org/TR/skos-reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1" s="49">
+      <c r="A48" s="158" t="inlineStr">
+        <is>
+          <t>Dublin Core</t>
+        </is>
+      </c>
+      <c r="B48" s="159" t="inlineStr">
+        <is>
+          <t>Title, creator, date, licence</t>
+        </is>
+      </c>
+      <c r="C48" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F48" s="159" t="inlineStr">
+        <is>
+          <t>Makes the ontology citable. Cheap</t>
+        </is>
+      </c>
+      <c r="G48" s="161" t="inlineStr">
+        <is>
+          <t>dublincore.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1" s="49">
+      <c r="A49" s="158" t="inlineStr">
+        <is>
+          <t>geo: and dbo:</t>
+        </is>
+      </c>
+      <c r="B49" s="159" t="inlineStr">
+        <is>
+          <t>Coordinates and DBpedia terms</t>
+        </is>
+      </c>
+      <c r="C49" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D49" s="159" t="inlineStr">
+        <is>
+          <t>Country to capital city to lat and long, for a map</t>
+        </is>
+      </c>
+      <c r="E49" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F49" s="159" t="inlineStr">
+        <is>
+          <t>Wikidata is better maintained now</t>
+        </is>
+      </c>
+      <c r="G49" s="161" t="inlineStr">
+        <is>
+          <t>dbpedia.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1" s="49">
+      <c r="A50" s="157" t="inlineStr">
+        <is>
+          <t>6. Outside data I link to</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1" s="49">
+      <c r="A51" s="158" t="inlineStr">
+        <is>
+          <t>CosIng</t>
+        </is>
+      </c>
+      <c r="B51" s="159" t="inlineStr">
+        <is>
+          <t>The EU official ingredient database</t>
+        </is>
+      </c>
+      <c r="C51" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F51" s="159" t="inlineStr">
+        <is>
+          <t>My ingredients get a legal status. The whole point</t>
+        </is>
+      </c>
+      <c r="G51" s="161" t="inlineStr">
+        <is>
+          <t>ec.europa.eu/growth/tools-databases/cosing</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1" s="49">
+      <c r="A52" s="158" t="inlineStr">
+        <is>
+          <t>CosIng-KG</t>
+        </is>
+      </c>
+      <c r="B52" s="159" t="inlineStr">
+        <is>
+          <t>CosIng already turned into RDF</t>
+        </is>
+      </c>
+      <c r="C52" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="160" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="F52" s="159" t="inlineStr">
+        <is>
+          <t>If it works I reuse it and save weeks</t>
+        </is>
+      </c>
+      <c r="G52" s="161" t="inlineStr">
+        <is>
+          <t>github.com/biobricks-ai/cosing-kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1" s="49">
+      <c r="A53" s="158" t="inlineStr">
+        <is>
+          <t>DermO</t>
+        </is>
+      </c>
+      <c r="B53" s="159" t="inlineStr">
+        <is>
+          <t>3,000 skin disease terms by dermatologists</t>
+        </is>
+      </c>
+      <c r="C53" s="159" t="inlineStr">
+        <is>
+          <t>DermO 2016</t>
+        </is>
+      </c>
+      <c r="D53" s="159" t="inlineStr">
+        <is>
+          <t>Built with OBO tooling and Protege, published on BioPortal</t>
+        </is>
+      </c>
+      <c r="E53" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F53" s="159" t="inlineStr">
+        <is>
+          <t>Fixes my medical claims in six lines</t>
+        </is>
+      </c>
+      <c r="G53" s="161" t="inlineStr">
+        <is>
+          <t>bioportal.bioontology.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1" s="49">
+      <c r="A54" s="158" t="inlineStr">
+        <is>
+          <t>TXPO</t>
+        </is>
+      </c>
+      <c r="B54" s="159" t="inlineStr">
+        <is>
+          <t>Toxic process ontology, from OBO</t>
+        </is>
+      </c>
+      <c r="C54" s="159" t="inlineStr">
+        <is>
+          <t>TOXIN KG</t>
+        </is>
+      </c>
+      <c r="D54" s="159" t="inlineStr">
+        <is>
+          <t>Used as the backbone of their graph</t>
+        </is>
+      </c>
+      <c r="E54" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" s="159" t="inlineStr">
+        <is>
+          <t>Too deep into toxicology mechanisms</t>
+        </is>
+      </c>
+      <c r="G54" s="161" t="inlineStr">
+        <is>
+          <t>obofoundry.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1" s="49">
+      <c r="A55" s="158" t="inlineStr">
+        <is>
+          <t>Wikidata</t>
+        </is>
+      </c>
+      <c r="B55" s="159" t="inlineStr">
+        <is>
+          <t>Wikipedia facts, queryable</t>
+        </is>
+      </c>
+      <c r="C55" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F55" s="159" t="inlineStr">
+        <is>
+          <t>Gives me brand ownership, one line per brand</t>
+        </is>
+      </c>
+      <c r="G55" s="161" t="inlineStr">
+        <is>
+          <t>wikidata.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1" s="49">
+      <c r="A56" s="158" t="inlineStr">
+        <is>
+          <t>DBpedia</t>
+        </is>
+      </c>
+      <c r="B56" s="159" t="inlineStr">
+        <is>
+          <t>Older Wikipedia graph</t>
+        </is>
+      </c>
+      <c r="C56" s="159" t="inlineStr">
+        <is>
+          <t>Abesova, Di Noia</t>
+        </is>
+      </c>
+      <c r="D56" s="159" t="inlineStr">
+        <is>
+          <t>Abesova pulled countries and map coordinates live</t>
+        </is>
+      </c>
+      <c r="E56" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F56" s="159" t="inlineStr">
+        <is>
+          <t>Wikidata is better maintained</t>
+        </is>
+      </c>
+      <c r="G56" s="161" t="inlineStr">
+        <is>
+          <t>dbpedia.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1" s="49">
+      <c r="A57" s="158" t="inlineStr">
+        <is>
+          <t>LOV</t>
+        </is>
+      </c>
+      <c r="B57" s="159" t="inlineStr">
+        <is>
+          <t>Search engine for existing vocabularies</t>
+        </is>
+      </c>
+      <c r="C57" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F57" s="159" t="inlineStr">
+        <is>
+          <t>Search before inventing a term. Amateur test</t>
+        </is>
+      </c>
+      <c r="G57" s="161" t="inlineStr">
+        <is>
+          <t>lov.linkeddata.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" s="49">
+      <c r="A58" s="157" t="inlineStr">
+        <is>
+          <t>7. Checking and publishing</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1" s="49">
+      <c r="A59" s="158" t="inlineStr">
+        <is>
+          <t>OOPS!</t>
+        </is>
+      </c>
+      <c r="B59" s="159" t="inlineStr">
+        <is>
+          <t>Free website that finds ontology errors</t>
+        </is>
+      </c>
+      <c r="C59" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" s="159" t="inlineStr">
+        <is>
+          <t>One afternoon buys a real evaluation section</t>
+        </is>
+      </c>
+      <c r="G59" s="161" t="inlineStr">
+        <is>
+          <t>oops.linkeddata.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1" s="49">
+      <c r="A60" s="158" t="inlineStr">
+        <is>
+          <t>FOOPS!</t>
+        </is>
+      </c>
+      <c r="B60" s="159" t="inlineStr">
+        <is>
+          <t>Scores how findable and reusable it is</t>
+        </is>
+      </c>
+      <c r="C60" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" s="159" t="inlineStr">
+        <is>
+          <t>I criticise everyone for not publishing</t>
+        </is>
+      </c>
+      <c r="G60" s="161" t="inlineStr">
+        <is>
+          <t>w3id.org/foops</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1" s="49">
+      <c r="A61" s="158" t="inlineStr">
+        <is>
+          <t>OntoMetrics</t>
+        </is>
+      </c>
+      <c r="B61" s="159" t="inlineStr">
+        <is>
+          <t>Depth, breadth, structural numbers</t>
+        </is>
+      </c>
+      <c r="C61" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" s="159" t="inlineStr">
+        <is>
+          <t>Comparable figures for the evaluation table</t>
+        </is>
+      </c>
+      <c r="G61" s="161" t="inlineStr">
+        <is>
+          <t>ontometrics.uni-rostock.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1" s="49">
+      <c r="A62" s="158" t="inlineStr">
+        <is>
+          <t>WIDOCO</t>
+        </is>
+      </c>
+      <c r="B62" s="159" t="inlineStr">
+        <is>
+          <t>Makes a docs page from the ontology</t>
+        </is>
+      </c>
+      <c r="C62" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F62" s="159" t="inlineStr">
+        <is>
+          <t>The docs cannot drift from the file</t>
+        </is>
+      </c>
+      <c r="G62" s="161" t="inlineStr">
+        <is>
+          <t>github.com/dgarijo/Widoco</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1" s="49">
+      <c r="A63" s="158" t="inlineStr">
+        <is>
+          <t>w3id.org</t>
+        </is>
+      </c>
+      <c r="B63" s="159" t="inlineStr">
+        <is>
+          <t>A permanent web address</t>
+        </is>
+      </c>
+      <c r="C63" s="159" t="inlineStr">
+        <is>
+          <t>OntoCosmetic</t>
+        </is>
+      </c>
+      <c r="D63" s="159" t="inlineStr">
+        <is>
+          <t>purl.org address that still works today</t>
+        </is>
+      </c>
+      <c r="E63" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F63" s="159" t="inlineStr">
+        <is>
+          <t>A university URL dies when I graduate</t>
+        </is>
+      </c>
+      <c r="G63" s="161" t="inlineStr">
+        <is>
+          <t>w3id.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1" s="49">
+      <c r="A64" s="158" t="inlineStr">
+        <is>
+          <t>Zenodo</t>
+        </is>
+      </c>
+      <c r="B64" s="159" t="inlineStr">
+        <is>
+          <t>Gives each release a DOI</t>
+        </is>
+      </c>
+      <c r="C64" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F64" s="159" t="inlineStr">
+        <is>
+          <t>1 in 6 competitors publishes. I will</t>
+        </is>
+      </c>
+      <c r="G64" s="161" t="inlineStr">
+        <is>
+          <t>zenodo.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" s="49">
+      <c r="A65" s="157" t="inlineStr">
+        <is>
+          <t>8. Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1" s="49">
+      <c r="A66" s="158" t="inlineStr">
+        <is>
+          <t>METHONTOLOGY</t>
+        </is>
+      </c>
+      <c r="B66" s="159" t="inlineStr">
+        <is>
+          <t>Older, document-heavy method</t>
+        </is>
+      </c>
+      <c r="C66" s="159" t="inlineStr">
+        <is>
+          <t>bit-Tech, Utari</t>
+        </is>
+      </c>
+      <c r="D66" s="159" t="inlineStr">
+        <is>
+          <t>Both named it as their method</t>
+        </is>
+      </c>
+      <c r="E66" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F66" s="159" t="inlineStr">
+        <is>
+          <t>Thorough but old. I take its glossary step</t>
+        </is>
+      </c>
+      <c r="G66" s="161" t="inlineStr">
+        <is>
+          <t>search: Fernandez-Lopez 1997</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1" s="49">
+      <c r="A67" s="158" t="inlineStr">
+        <is>
+          <t>Middle-out</t>
+        </is>
+      </c>
+      <c r="B67" s="159" t="inlineStr">
+        <is>
+          <t>Start in the middle, grow both ways</t>
+        </is>
+      </c>
+      <c r="C67" s="159" t="inlineStr">
+        <is>
+          <t>Abesova</t>
+        </is>
+      </c>
+      <c r="D67" s="159" t="inlineStr">
+        <is>
+          <t>Started from a base ontology, let the CSV widen it</t>
+        </is>
+      </c>
+      <c r="E67" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F67" s="159" t="inlineStr">
+        <is>
+          <t>Honest, but it is what you do by accident</t>
+        </is>
+      </c>
+      <c r="G67" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1" s="49">
+      <c r="A68" s="158" t="inlineStr">
+        <is>
+          <t>MOMo</t>
+        </is>
+      </c>
+      <c r="B68" s="159" t="inlineStr">
+        <is>
+          <t>Modular ontology modeling</t>
+        </is>
+      </c>
+      <c r="C68" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" s="159" t="inlineStr">
+        <is>
+          <t>My four modules follow it</t>
+        </is>
+      </c>
+      <c r="G68" s="161" t="inlineStr">
+        <is>
+          <t>search: Shimizu MOMo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1" s="49">
+      <c r="A69" s="158" t="inlineStr">
+        <is>
+          <t>LOT</t>
+        </is>
+      </c>
+      <c r="B69" s="159" t="inlineStr">
+        <is>
+          <t>Linked Open Terms. Four steps</t>
+        </is>
+      </c>
+      <c r="C69" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F69" s="159" t="inlineStr">
+        <is>
+          <t>Built around reuse and publishing</t>
+        </is>
+      </c>
+      <c r="G69" s="161" t="inlineStr">
+        <is>
+          <t>lot.linkeddata.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1" s="49">
+      <c r="A70" s="158" t="inlineStr">
+        <is>
+          <t>Noy &amp; McGuinness 101</t>
+        </is>
+      </c>
+      <c r="B70" s="159" t="inlineStr">
+        <is>
+          <t>The classic seven-step guide</t>
+        </is>
+      </c>
+      <c r="C70" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="160" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+      <c r="F70" s="159" t="inlineStr">
+        <is>
+          <t>Everyone cites it. Too light to be my method</t>
+        </is>
+      </c>
+      <c r="G70" s="161" t="inlineStr">
+        <is>
+          <t>protege.stanford.edu/publications</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1" s="49">
+      <c r="A71" s="158" t="inlineStr">
+        <is>
+          <t>Competency questions</t>
+        </is>
+      </c>
+      <c r="B71" s="159" t="inlineStr">
+        <is>
+          <t>Questions the ontology must answer</t>
+        </is>
+      </c>
+      <c r="C71" s="159" t="inlineStr">
+        <is>
+          <t>COPPER</t>
+        </is>
+      </c>
+      <c r="D71" s="159" t="inlineStr">
+        <is>
+          <t>Used them as one of three evaluation layers</t>
+        </is>
+      </c>
+      <c r="E71" s="160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F71" s="159" t="inlineStr">
+        <is>
+          <t>Turns 'is it good' into something testable</t>
+        </is>
+      </c>
+      <c r="G71" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1" s="49">
+      <c r="A72" s="158" t="inlineStr">
+        <is>
+          <t>OBO principles</t>
+        </is>
+      </c>
+      <c r="B72" s="159" t="inlineStr">
+        <is>
+          <t>Rules for building shared ontologies</t>
+        </is>
+      </c>
+      <c r="C72" s="159" t="inlineStr">
+        <is>
+          <t>COPPER, DermO</t>
+        </is>
+      </c>
+      <c r="D72" s="159" t="inlineStr">
+        <is>
+          <t>COPPER checked its process against them</t>
+        </is>
+      </c>
+      <c r="E72" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F72" s="159" t="inlineStr">
+        <is>
+          <t>Good practice to cite even if I do not join</t>
+        </is>
+      </c>
+      <c r="G72" s="161" t="inlineStr">
+        <is>
+          <t>obofoundry.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1" s="49">
+      <c r="A73" s="157" t="inlineStr">
+        <is>
+          <t>9. Used by the papers, not by me</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1" s="49">
+      <c r="A74" s="158" t="inlineStr">
+        <is>
+          <t>CCBR</t>
+        </is>
+      </c>
+      <c r="B74" s="159" t="inlineStr">
+        <is>
+          <t>Conversational case-based reasoning</t>
+        </is>
+      </c>
+      <c r="C74" s="159" t="inlineStr">
+        <is>
+          <t>Moe &amp; Aung</t>
+        </is>
+      </c>
+      <c r="D74" s="159" t="inlineStr">
+        <is>
+          <t>Six questions turn a vague complaint into a query</t>
+        </is>
+      </c>
+      <c r="E74" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" s="159" t="inlineStr">
+        <is>
+          <t>Needs a hand-built case base</t>
+        </is>
+      </c>
+      <c r="G74" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1" s="49">
+      <c r="A75" s="158" t="inlineStr">
+        <is>
+          <t>Ford-Fulkerson</t>
+        </is>
+      </c>
+      <c r="B75" s="159" t="inlineStr">
+        <is>
+          <t>A max-flow algorithm</t>
+        </is>
+      </c>
+      <c r="C75" s="159" t="inlineStr">
+        <is>
+          <t>Moe &amp; Aung</t>
+        </is>
+      </c>
+      <c r="D75" s="159" t="inlineStr">
+        <is>
+          <t>Scored products by how much need they satisfy</t>
+        </is>
+      </c>
+      <c r="E75" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" s="159" t="inlineStr">
+        <is>
+          <t>A weighted filter does the same for me</t>
+        </is>
+      </c>
+      <c r="G75" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1" s="49">
+      <c r="A76" s="158" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B76" s="159" t="inlineStr">
+        <is>
+          <t>Neural net that reads images</t>
+        </is>
+      </c>
+      <c r="C76" s="159" t="inlineStr">
+        <is>
+          <t>Hansanie, Lee (lululab)</t>
+        </is>
+      </c>
+      <c r="D76" s="159" t="inlineStr">
+        <is>
+          <t>Graded acne from a face photo</t>
+        </is>
+      </c>
+      <c r="E76" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" s="159" t="inlineStr">
+        <is>
+          <t>No photos, no ethics approval</t>
+        </is>
+      </c>
+      <c r="G76" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19" customHeight="1" s="49">
+      <c r="A77" s="158" t="inlineStr">
+        <is>
+          <t>Graph attention network</t>
+        </is>
+      </c>
+      <c r="B77" s="159" t="inlineStr">
+        <is>
+          <t>Neural net over a graph</t>
+        </is>
+      </c>
+      <c r="C77" s="159" t="inlineStr">
+        <is>
+          <t>HaCKG</t>
+        </is>
+      </c>
+      <c r="D77" s="159" t="inlineStr">
+        <is>
+          <t>Predicted halal status from the graph</t>
+        </is>
+      </c>
+      <c r="E77" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F77" s="159" t="inlineStr">
+        <is>
+          <t>Future work. Needs interaction data</t>
+        </is>
+      </c>
+      <c r="G77" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1" s="49">
+      <c r="A78" s="158" t="inlineStr">
+        <is>
+          <t>AHP</t>
+        </is>
+      </c>
+      <c r="B78" s="159" t="inlineStr">
+        <is>
+          <t>Weigh criteria by comparing in pairs</t>
+        </is>
+      </c>
+      <c r="C78" s="159" t="inlineStr">
+        <is>
+          <t>OntoCosmetic</t>
+        </is>
+      </c>
+      <c r="D78" s="159" t="inlineStr">
+        <is>
+          <t>Ranked ingredients on several properties at once</t>
+        </is>
+      </c>
+      <c r="E78" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F78" s="159" t="inlineStr">
+        <is>
+          <t>Could rank on price and availability</t>
+        </is>
+      </c>
+      <c r="G78" s="161" t="inlineStr">
+        <is>
+          <t>search: Saaty AHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="19" customHeight="1" s="49">
+      <c r="A79" s="158" t="inlineStr">
+        <is>
+          <t>AttrakDiff</t>
+        </is>
+      </c>
+      <c r="B79" s="159" t="inlineStr">
+        <is>
+          <t>User experience questionnaire</t>
+        </is>
+      </c>
+      <c r="C79" s="159" t="inlineStr">
+        <is>
+          <t>OntoCosmetic</t>
+        </is>
+      </c>
+      <c r="D79" s="159" t="inlineStr">
+        <is>
+          <t>Ran it between design iterations</t>
+        </is>
+      </c>
+      <c r="E79" s="160" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="F79" s="159" t="inlineStr">
+        <is>
+          <t>Only if I build an interface</t>
+        </is>
+      </c>
+      <c r="G79" s="161" t="inlineStr">
+        <is>
+          <t>attrakdiff.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1" s="49">
+      <c r="A80" s="158" t="inlineStr">
+        <is>
+          <t>SUS and MAE</t>
+        </is>
+      </c>
+      <c r="B80" s="159" t="inlineStr">
+        <is>
+          <t>Usability score, and rating error</t>
+        </is>
+      </c>
+      <c r="C80" s="159" t="inlineStr">
+        <is>
+          <t>Mahadewi</t>
+        </is>
+      </c>
+      <c r="D80" s="159" t="inlineStr">
+        <is>
+          <t>The two numbers they report</t>
+        </is>
+      </c>
+      <c r="E80" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F80" s="159" t="inlineStr">
+        <is>
+          <t>FEVR says match evaluation to the goal</t>
+        </is>
+      </c>
+      <c r="G80" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="19" customHeight="1" s="49">
+      <c r="A81" s="158" t="inlineStr">
+        <is>
+          <t>Slope One</t>
+        </is>
+      </c>
+      <c r="B81" s="159" t="inlineStr">
+        <is>
+          <t>Simple collaborative filtering</t>
+        </is>
+      </c>
+      <c r="C81" s="159" t="inlineStr">
+        <is>
+          <t>Mahadewi</t>
+        </is>
+      </c>
+      <c r="D81" s="159" t="inlineStr">
+        <is>
+          <t>Predicted ratings from item differences</t>
+        </is>
+      </c>
+      <c r="E81" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F81" s="159" t="inlineStr">
+        <is>
+          <t>Needs a ratings matrix I do not have</t>
+        </is>
+      </c>
+      <c r="G81" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1" s="49">
+      <c r="A82" s="158" t="inlineStr">
+        <is>
+          <t>Precision / recall / F</t>
+        </is>
+      </c>
+      <c r="B82" s="159" t="inlineStr">
+        <is>
+          <t>Standard accuracy measures</t>
+        </is>
+      </c>
+      <c r="C82" s="159" t="inlineStr">
+        <is>
+          <t>Moe &amp; Aung, Hansanie, E-Prod</t>
+        </is>
+      </c>
+      <c r="D82" s="159" t="inlineStr">
+        <is>
+          <t>Reported as the whole evaluation</t>
+        </is>
+      </c>
+      <c r="E82" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F82" s="159" t="inlineStr">
+        <is>
+          <t>Wrong measure for a knowledge graph</t>
+        </is>
+      </c>
+      <c r="G82" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1" s="49">
+      <c r="A83" s="158" t="inlineStr">
+        <is>
+          <t>Sequential pattern mining</t>
+        </is>
+      </c>
+      <c r="B83" s="159" t="inlineStr">
+        <is>
+          <t>Finds common orderings</t>
+        </is>
+      </c>
+      <c r="C83" s="159" t="inlineStr">
+        <is>
+          <t>Tarus</t>
+        </is>
+      </c>
+      <c r="D83" s="159" t="inlineStr">
+        <is>
+          <t>Learned the order people consume things in</t>
+        </is>
+      </c>
+      <c r="E83" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F83" s="159" t="inlineStr">
+        <is>
+          <t>My routine_step does this by rule</t>
+        </is>
+      </c>
+      <c r="G83" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1" s="49">
+      <c r="A84" s="158" t="inlineStr">
+        <is>
+          <t>SMILES</t>
+        </is>
+      </c>
+      <c r="B84" s="159" t="inlineStr">
+        <is>
+          <t>Text form of a molecule's structure</t>
+        </is>
+      </c>
+      <c r="C84" s="159" t="inlineStr">
+        <is>
+          <t>TOXIN KG</t>
+        </is>
+      </c>
+      <c r="D84" s="159" t="inlineStr">
+        <is>
+          <t>Every chemical gets a structure string</t>
+        </is>
+      </c>
+      <c r="E84" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F84" s="159" t="inlineStr">
+        <is>
+          <t>I have CAS numbers from CosIng</t>
+        </is>
+      </c>
+      <c r="G84" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1" s="49">
+      <c r="A85" s="158" t="inlineStr">
+        <is>
+          <t>GraphRAG</t>
+        </is>
+      </c>
+      <c r="B85" s="159" t="inlineStr">
+        <is>
+          <t>Ontology-grounded graph feeding an LLM</t>
+        </is>
+      </c>
+      <c r="C85" s="159" t="inlineStr">
+        <is>
+          <t>Ali 2026</t>
+        </is>
+      </c>
+      <c r="D85" s="159" t="inlineStr">
+        <is>
+          <t>The graph stops the model inventing answers</t>
+        </is>
+      </c>
+      <c r="E85" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F85" s="159" t="inlineStr">
+        <is>
+          <t>My future work chapter</t>
+        </is>
+      </c>
+      <c r="G85" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19" customHeight="1" s="49">
+      <c r="A86" s="158" t="inlineStr">
         <is>
           <t>Tkinter</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Python's basic window toolkit</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Hansanie &amp; Silva built their desktop app with it</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>docs.python.org/3/library/tkinter.html</t>
-        </is>
-      </c>
-      <c r="F19" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>We are not building a desktop app</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="49">
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REASONERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1" s="49">
-      <c r="B21" s="42" t="inlineStr">
-        <is>
-          <t>HermiT</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>A reasoner. Reads the ontology and works out what follows, and finds contradictions</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Fills the defined classes. Flags the 593 sensitive-skin products that contain an allergen</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>hermit-reasoner.com</t>
-        </is>
-      </c>
-      <c r="F21" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Ships with Protégé, solid default. Does NOT run SWRL rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1" s="49">
-      <c r="B22" s="42" t="inlineStr">
-        <is>
-          <t>Pellet / Openllet</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Another reasoner. Openllet is the maintained version</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Same job, but it also runs SWRL rules. Hansanie &amp; Silva used Pellet</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>github.com/Galigator/openllet</t>
-        </is>
-      </c>
-      <c r="F22" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Only if we write SWRL rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1" s="49">
-      <c r="B23" s="42" t="inlineStr">
-        <is>
-          <t>ELK</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>A very fast reasoner for a simple subset of OWL</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Used by the big biomedical ontologies</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>github.com/liveontologies/elk-reasoner</t>
-        </is>
-      </c>
-      <c r="F23" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Too limited for our defined classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" s="49">
-      <c r="B24" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DATABASES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1" s="49">
-      <c r="B25" s="42" t="inlineStr">
-        <is>
-          <t>GraphDB</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>A database for triples with SPARQL on the front and a picture of the graph</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Stores our 1.8 million triples in named boxes per source. Abesova used it</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>graphdb.ontotext.com</t>
-        </is>
-      </c>
-      <c r="F25" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Free desktop edition, reasoning built in, and the visual explorer is worth more in a meeting than any paragraph</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1" s="49">
-      <c r="B26" s="42" t="inlineStr">
-        <is>
-          <t>Apache Jena Fuseki</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>A free, simpler triple store</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Same job as GraphDB. bit-Tech used it</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>jena.apache.org/documentation/fuseki2</t>
-        </is>
-      </c>
-      <c r="F26" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Simpler, but its reasoning is weak and it has no visual explorer. GraphDB does more for the same price</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1" s="49">
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>Stardog / Virtuoso</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Commercial triple stores. Virtuoso runs DBpedia itself</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Same job, bigger scale</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>stardog.com, virtuoso.openlinksw.com</t>
-        </is>
-      </c>
-      <c r="F27" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>We do not need the scale and Stardog costs money</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="46" customHeight="1" s="49">
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>OntoRefine</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>A point-and-click tool inside GraphDB that turns a CSV into triples</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Abesova's team used it to map Sephora columns to classes</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>graphdb.ontotext.com/documentation</t>
-        </is>
-      </c>
-      <c r="F28" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Good, but the mapping is trapped inside GraphDB. Morph-KGC's mapping is a file we can put in the appendix</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="46" customHeight="1" s="49">
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>Morph-KGC</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>The Python engine that reads an RML mapping and writes the triples</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>One command turns our CSV into the graph. Rerun it whenever the data changes</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>morph-kgc.readthedocs.io</t>
-        </is>
-      </c>
-      <c r="F29" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Python, fast on big CSVs, and the mapping is auditable. This is our population tool</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" s="49">
-      <c r="B30" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VOCABULARIES WE REUSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="46" customHeight="1" s="49">
-      <c r="B31" s="42" t="inlineStr">
-        <is>
-          <t>schema.org</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>The vocabulary Google uses for products and shops</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Gives us Product, Offer, price, brand, seller. Splits the product from the offer, which is how one lotion holds two prices</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>schema.org</t>
-        </is>
-      </c>
-      <c r="F31" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Everyone understands it already. No point inventing our own word for 'price'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="46" customHeight="1" s="49">
-      <c r="B32" s="42" t="inlineStr">
-        <is>
-          <t>PROV-O</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>A W3C standard for saying where information came from</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>wasAttributedTo, wasDerivedFrom, generatedAtTime. Our four evidence levels in a language other people speak</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>w3.org/TR/prov-o</t>
-        </is>
-      </c>
-      <c r="F32" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Turns our most original design choice into a standard one. O'Sullivan 2025 did exactly this</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1" s="49">
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>SKOS</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>For lists of words that are labels, not objects</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Our benefits: 'Hydrating' and 'Hydration' become one concept with two labels</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>w3.org/TR/skos-reference</t>
-        </is>
-      </c>
-      <c r="F33" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Benefits are terms people use, not logical classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1" s="49">
-      <c r="B34" s="42" t="inlineStr">
-        <is>
-          <t>Dublin Core</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>The basic bookkeeping vocabulary: title, creator, licence, date</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Makes the dataset and ontology citable</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>dublincore.org</t>
-        </is>
-      </c>
-      <c r="F34" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Cheap and expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" s="49">
-      <c r="B35" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OUTSIDE DATA WE LINK TO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46" customHeight="1" s="49">
-      <c r="B36" s="42" t="inlineStr">
-        <is>
-          <t>CosIng</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>The European Commission's official cosmetic ingredient register, 28,573 entries</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Our ingredients get a legal status from it. Already linked on 99.2% of products with a formula</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>ec.europa.eu/growth/tools-databases/cosing</t>
-        </is>
-      </c>
-      <c r="F36" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>It is the whole point</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="46" customHeight="1" s="49">
-      <c r="B37" s="42" t="inlineStr">
-        <is>
-          <t>CosIng-KG</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>CosIng already converted to RDF, on GitHub</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Could be our entire ingredient layer for free</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>github.com/biobricks-ai/cosing-kg</t>
-        </is>
-      </c>
-      <c r="F37" s="46" t="inlineStr">
-        <is>
-          <t>CHECK FIRST</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>If usable, we cite it and save weeks. If not, our own conversion is a contribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1" s="49">
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t>DermO</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>3,000 skin disease terms written by dermatologists, on BioPortal</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Our concerns (eczema, rosacea, acne) point at real clinical terms aligned to ICD-10</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>bioportal.bioontology.org/ontologies/DERMO</t>
-        </is>
-      </c>
-      <c r="F38" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Six lines of alignment fix the fact that no clinician has checked our vocabulary</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="46" customHeight="1" s="49">
-      <c r="B39" s="42" t="inlineStr">
-        <is>
-          <t>Wikidata</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Wikipedia's facts as a queryable graph</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Tells us who owns each brand. L'Oreal owns 570 of our products</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>wikidata.org</t>
-        </is>
-      </c>
-      <c r="F39" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>One line per brand, and we get ownership and country for free</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="46" customHeight="1" s="49">
-      <c r="B40" s="42" t="inlineStr">
-        <is>
-          <t>DBpedia</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Wikipedia turned into a graph, older cousin of Wikidata</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Abesova pulled countries and map coordinates from it</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>dbpedia.org</t>
-        </is>
-      </c>
-      <c r="F40" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Wikidata is better maintained now</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="46" customHeight="1" s="49">
-      <c r="B41" s="42" t="inlineStr">
-        <is>
-          <t>BioPortal / OBO Foundry</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Where biomedical ontologies live. OBO is the community with shared rules</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>DermO is on BioPortal. TOXIN reused TXPO from OBO</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>bioportal.bioontology.org</t>
-        </is>
-      </c>
-      <c r="F41" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>We fetch DermO from here</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="46" customHeight="1" s="49">
-      <c r="B42" s="42" t="inlineStr">
-        <is>
-          <t>Linked Open Vocabularies (LOV)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>A search engine for existing vocabulary terms</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Search 'price' before inventing skc:price</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>lov.linkeddata.es</t>
-        </is>
-      </c>
-      <c r="F42" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>The one habit that separates an amateur ontology from a professional one</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1" s="49">
-      <c r="B43" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CHECKING AND PUBLISHING</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="46" customHeight="1" s="49">
-      <c r="B44" s="42" t="inlineStr">
-        <is>
-          <t>OOPS!</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>A free website that checks your ontology against 41 known design mistakes</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Paste the file, get a graded list: critical, important, minor</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>oops.linkeddata.es</t>
-        </is>
-      </c>
-      <c r="F44" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>One afternoon for a real evaluation number nobody in group A has</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="46" customHeight="1" s="49">
-      <c r="B45" s="42" t="inlineStr">
-        <is>
-          <t>FOOPS!</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>A free website that scores how FAIR your ontology is (findable, accessible, interoperable, reusable)</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>24 checks, a score, and what is missing</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>w3id.org/foops</t>
-        </is>
-      </c>
-      <c r="F45" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>We criticise everyone for not publishing, so we measure our own</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="46" customHeight="1" s="49">
-      <c r="B46" s="42" t="inlineStr">
-        <is>
-          <t>OntoMetrics</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Structural numbers: depth, breadth, richness</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Comparable figures for the evaluation table</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>ontometrics.uni-rostock.de</t>
-        </is>
-      </c>
-      <c r="F46" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Cheap and standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="46" customHeight="1" s="49">
-      <c r="B47" s="42" t="inlineStr">
-        <is>
-          <t>WIDOCO</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Makes a documentation web page from the ontology file</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>So the docs cannot drift from the code</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>github.com/dgarijo/Widoco</t>
-        </is>
-      </c>
-      <c r="F47" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Free, and it is what the w3id address will point at</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="46" customHeight="1" s="49">
-      <c r="B48" s="42" t="inlineStr">
-        <is>
-          <t>w3id.org</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>A permanent web address for your ontology</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Survives you leaving BAU. It is a pull request on GitHub</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>w3id.org</t>
-        </is>
-      </c>
-      <c r="F48" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>A university URL dies when you graduate</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="46" customHeight="1" s="49">
-      <c r="B49" s="42" t="inlineStr">
-        <is>
-          <t>Zenodo</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Gives a DOI to each release</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>The ontology becomes citable like a paper</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>zenodo.org</t>
-        </is>
-      </c>
-      <c r="F49" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>One in six competitors publishes. This is how we do it properly</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" s="49">
-      <c r="B50" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHODS</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="46" customHeight="1" s="49">
-      <c r="B51" s="42" t="inlineStr">
-        <is>
-          <t>METHONTOLOGY</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>An older, document-heavy method: glossary, taxonomies, relation diagrams, concept dictionary</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>The default in this field. bit-Tech, Utari and Mahadewi all use it. Moe &amp; Aung follow it without naming it</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>search: METHONTOLOGY Fernandez-Lopez 1997</t>
-        </is>
-      </c>
-      <c r="F51" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Thorough but old. We take its glossary step and use MOMo + LOT instead, with a stated reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1" s="49">
-      <c r="B52" s="42" t="inlineStr">
-        <is>
-          <t>MOMo</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Modular Ontology Modeling. Build in modules using design patterns, draw before you write</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Our four-module design follows it</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>search: Shimizu Modular Ontology Modeling 2022</t>
-        </is>
-      </c>
-      <c r="F52" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Names four reasons reuse fails and we have hit three of them</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="46" customHeight="1" s="49">
-      <c r="B53" s="42" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Linked Open Terms. Four steps: requirements, build, publish, maintain</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Our project structure and publication discipline</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>lot.linkeddata.es</t>
-        </is>
-      </c>
-      <c r="F53" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Built around reusing terms and publishing, which are the two things this field is worst at</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="46" customHeight="1" s="49">
-      <c r="B54" s="42" t="inlineStr">
-        <is>
-          <t>Ontology Development 101</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Noy &amp; McGuinness 2001, the seven-step teaching guide</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Its class-vs-individual test told us Annex entries are individuals</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>protege.stanford.edu/publications/ontology_development/ontology101.pdf</t>
-        </is>
-      </c>
-      <c r="F54" s="47" t="inlineStr">
-        <is>
-          <t>CITE</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Everyone cites it. Too light to be our only method</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="46" customHeight="1" s="49">
-      <c r="B55" s="42" t="inlineStr">
-        <is>
-          <t>Competency questions</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Questions the ontology must be able to answer, written BEFORE building</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Our 15 questions become our 15 SPARQL queries become our evaluation chapter. COPPER did the same</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>in 06_ontology_master_plan.md</t>
-        </is>
-      </c>
-      <c r="F55" s="43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Turns 'is it good' into something measurable</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1" s="49">
-      <c r="B56" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THINGS THE PAPERS USED THAT WE DON'T</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="46" customHeight="1" s="49">
-      <c r="B57" s="42" t="inlineStr">
-        <is>
-          <t>CCBR</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Conversational case-based reasoning. Narrow a problem by asking questions, like a doctor</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Moe &amp; Aung: six questions turn 'I have acne' into 'papules'</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>in the Moe &amp; Aung paper</t>
-        </is>
-      </c>
-      <c r="F57" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>Needs a hand-built case base and a dermatologist</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="46" customHeight="1" s="49">
-      <c r="B58" s="42" t="inlineStr">
-        <is>
-          <t>Ford-Fulkerson</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>A maximum-flow algorithm. Water through pipes</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Moe &amp; Aung score products by how much flow reaches them</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>search: Ford-Fulkerson algorithm</t>
-        </is>
-      </c>
-      <c r="F58" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>A weighted filter does the same for us with less machinery</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="46" customHeight="1" s="49">
-      <c r="B59" s="42" t="inlineStr">
-        <is>
-          <t>CNN</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Convolutional neural network, a model that reads images</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Hansanie &amp; Silva grade acne from a photo. Lee et al. read the face</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>search: convolutional neural network</t>
-        </is>
-      </c>
-      <c r="F59" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>No photos, no ethics approval. Could plug in later</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="46" customHeight="1" s="49">
-      <c r="B60" s="42" t="inlineStr">
-        <is>
-          <t>Graph attention network</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>A neural net that passes messages between connected nodes</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>HaCKG predicts halal status with one</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>search: relational graph attention network</t>
-        </is>
-      </c>
-      <c r="F60" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Future work. Needs interaction data</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="46" customHeight="1" s="49">
-      <c r="B61" s="42" t="inlineStr">
-        <is>
-          <t>AHP</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Analytic Hierarchy Process. Weigh several criteria by comparing them in pairs</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Formultools ranks ingredients on performance, origin and price with it</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>search: Saaty AHP 1987</t>
-        </is>
-      </c>
-      <c r="F61" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Could rank products on price, availability and evidence. Not needed yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="46" customHeight="1" s="49">
-      <c r="B62" s="42" t="inlineStr">
-        <is>
-          <t>AttrakDiff / SUS</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Standard questionnaires for user experience and usability</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Formultools used AttrakDiff between iterations. Mahadewi reported SUS 82</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>attrakdiff.de, search: System Usability Scale</t>
-        </is>
-      </c>
-      <c r="F62" s="44" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>If we ever build an interface. Cheap and standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="46" customHeight="1" s="49">
-      <c r="B63" s="42" t="inlineStr">
-        <is>
-          <t>Precision, recall, F-measure, MAE</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Standard accuracy measures</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Moe &amp; Aung, Hansanie, E-Prod and Mahadewi all report some of these</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>any ML textbook</t>
-        </is>
-      </c>
-      <c r="F63" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>FEVR says match the evaluation to the goal. Ours is verifiable correctness, so competency questions and consistency instead</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="46" customHeight="1" s="49">
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t>Slope One</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>A simple collaborative filtering algorithm</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Mahadewi predicts ratings with it</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>search: Slope One</t>
-        </is>
-      </c>
-      <c r="F64" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>Needs a ratings matrix we do not have</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="46" customHeight="1" s="49">
-      <c r="B65" s="42" t="inlineStr">
-        <is>
-          <t>SMILES</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>A text way of writing a molecule's structure</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>TOXIN adds it so every chemical has one identity</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>search: SMILES chemistry</t>
-        </is>
-      </c>
-      <c r="F65" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>We have CAS numbers from CosIng, same job</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="46" customHeight="1" s="49">
-      <c r="B66" s="42" t="inlineStr">
-        <is>
-          <t>TXPO</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>The ToXic Process Ontology from OBO Foundry</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>TOXIN's backbone ontology</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>obofoundry.org</t>
-        </is>
-      </c>
-      <c r="F66" s="45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Too deep into toxicology mechanisms for us</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="26" customHeight="1" s="49">
-      <c r="B68" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EDITORS INSTEAD OF PROTEGE   (my supervisor asked. 5 of my 28 papers used no Protege at all)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="58" customHeight="1" s="49">
-      <c r="B69" s="81" t="inlineStr">
-        <is>
-          <t>WebProtege</t>
-        </is>
-      </c>
-      <c r="C69" s="82" t="inlineStr">
-        <is>
-          <t>Protege in a browser, multi-user</t>
-        </is>
-      </c>
-      <c r="D69" s="82" t="inlineStr">
-        <is>
-          <t>Same model as Protege but two people can edit at once, with change history and comments. Handles thousands of classes.</t>
-        </is>
-      </c>
-      <c r="E69" s="83" t="inlineStr">
-        <is>
-          <t>webprotege.stanford.edu</t>
-        </is>
-      </c>
-      <c r="F69" s="84" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G69" s="85" t="inlineStr">
-        <is>
-          <t>Useful if my supervisor wants to comment directly on the ontology instead of by email. Weaker than desktop Protege for reasoning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="58" customHeight="1" s="49">
-      <c r="B70" s="86" t="inlineStr">
-        <is>
-          <t>OntoRefine</t>
-        </is>
-      </c>
-      <c r="C70" s="87" t="inlineStr">
-        <is>
-          <t>Point-and-click CSV to RDF, inside GraphDB</t>
-        </is>
-      </c>
-      <c r="D70" s="87" t="inlineStr">
-        <is>
-          <t>You see your spreadsheet, you draw which column becomes a subject and which becomes a predicate, it writes the RDF.</t>
-        </is>
-      </c>
-      <c r="E70" s="88" t="inlineStr">
-        <is>
-          <t>graphdb.ontotext.com</t>
-        </is>
-      </c>
-      <c r="F70" s="89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G70" s="90" t="inlineStr">
-        <is>
-          <t>ABESOVA USED THIS INSTEAD OF PROTEGE. It works, but the mapping is trapped inside GraphDB. I cannot put it in an appendix or re-run it from a script. Morph-KGC does the same job as a file I can publish.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="58" customHeight="1" s="49">
-      <c r="B71" s="81" t="inlineStr">
-        <is>
-          <t>TopBraid Composer / EDG</t>
-        </is>
-      </c>
-      <c r="C71" s="82" t="inlineStr">
-        <is>
-          <t>The commercial editor, from the people who wrote SHACL</t>
-        </is>
-      </c>
-      <c r="D71" s="82" t="inlineStr">
-        <is>
-          <t>Full OWL editing plus the best SHACL support anywhere. EDG adds governance and workflows.</t>
-        </is>
-      </c>
-      <c r="E71" s="83" t="inlineStr">
-        <is>
-          <t>topquadrant.com</t>
-        </is>
-      </c>
-      <c r="F71" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G71" s="85" t="inlineStr">
-        <is>
-          <t>The reference implementation for SHACL, so worth knowing it exists. But commercial, and I do not need governance workflows for a one-person thesis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="58" customHeight="1" s="49">
-      <c r="B72" s="86" t="inlineStr">
-        <is>
-          <t>VocBench 3</t>
-        </is>
-      </c>
-      <c r="C72" s="87" t="inlineStr">
-        <is>
-          <t>Web platform for vocabularies and thesauri</t>
-        </is>
-      </c>
-      <c r="D72" s="87" t="inlineStr">
-        <is>
-          <t>Strong on SKOS, multilingual labels, and editorial workflow. Almost full OWL 2 coverage.</t>
-        </is>
-      </c>
-      <c r="E72" s="88" t="inlineStr">
-        <is>
-          <t>vocbench.uniroma2.it</t>
-        </is>
-      </c>
-      <c r="F72" s="89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G72" s="91" t="inlineStr">
-        <is>
-          <t>Built for thesauri, not for defined classes. My benefits list is SKOS so it would suit that one part, but not the rest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="58" customHeight="1" s="49">
-      <c r="B73" s="81" t="inlineStr">
-        <is>
-          <t>ROBOT</t>
-        </is>
-      </c>
-      <c r="C73" s="82" t="inlineStr">
-        <is>
-          <t>A command-line tool for ontology jobs, from the OBO world</t>
-        </is>
-      </c>
-      <c r="D73" s="82" t="inlineStr">
-        <is>
-          <t>Convert formats, run a reasoner, extract a module, run quality reports. All from a script, no clicking.</t>
-        </is>
-      </c>
-      <c r="E73" s="83" t="inlineStr">
-        <is>
-          <t>github.com/ontodev/robot</t>
-        </is>
-      </c>
-      <c r="F73" s="84" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G73" s="85" t="inlineStr">
-        <is>
-          <t>This is how the serious biomedical ontologies are actually built. If I want my build to be repeatable rather than 'I clicked some things in Protege', this is the answer. Paper: Jackson et al., BMC Bioinformatics 2019.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="58" customHeight="1" s="49">
-      <c r="B74" s="86" t="inlineStr">
-        <is>
-          <t>LinkML</t>
-        </is>
-      </c>
-      <c r="C74" s="87" t="inlineStr">
-        <is>
-          <t>Write the model in YAML, generate everything else</t>
-        </is>
-      </c>
-      <c r="D74" s="87" t="inlineStr">
-        <is>
-          <t>One YAML schema generates OWL, SHACL, JSON Schema, Python classes and docs together.</t>
-        </is>
-      </c>
-      <c r="E74" s="88" t="inlineStr">
-        <is>
-          <t>linkml.io</t>
-        </is>
-      </c>
-      <c r="F74" s="89" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G74" s="91" t="inlineStr">
-        <is>
-          <t>Tempting, because it would give me OWL and SHACL from one source with no chance of them drifting apart. But it is another thing to learn and my ontology is small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="58" customHeight="1" s="49">
-      <c r="B75" s="81" t="inlineStr">
-        <is>
-          <t>Chowlk</t>
-        </is>
-      </c>
-      <c r="C75" s="82" t="inlineStr">
-        <is>
-          <t>Turn a diagram into OWL</t>
-        </is>
-      </c>
-      <c r="D75" s="82" t="inlineStr">
-        <is>
-          <t>You draw the ontology in diagrams.net using their notation, it outputs the OWL file.</t>
-        </is>
-      </c>
-      <c r="E75" s="83" t="inlineStr">
-        <is>
-          <t>chowlk.linkeddata.es</t>
-        </is>
-      </c>
-      <c r="F75" s="84" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G75" s="85" t="inlineStr">
-        <is>
-          <t>My chapter needs diagrams anyway. Drawing once and getting both the picture and the file is attractive. Same idea as CoModIDE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="58" customHeight="1" s="49">
-      <c r="B76" s="86" t="inlineStr">
-        <is>
-          <t>OWLGrEd</t>
-        </is>
-      </c>
-      <c r="C76" s="87" t="inlineStr">
-        <is>
-          <t>Draws an existing ontology as a UML-style picture</t>
-        </is>
-      </c>
-      <c r="D76" s="87" t="inlineStr">
-        <is>
-          <t>Point it at the OWL file, get a compact diagram of the whole thing.</t>
-        </is>
-      </c>
-      <c r="E76" s="88" t="inlineStr">
-        <is>
-          <t>owlgred.lumii.lv</t>
-        </is>
-      </c>
-      <c r="F76" s="89" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G76" s="91" t="inlineStr">
-        <is>
-          <t>Only for producing the figure in the chapter. Not for building.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="58" customHeight="1" s="49">
-      <c r="B77" s="81" t="inlineStr">
-        <is>
-          <t>Fluent Editor</t>
-        </is>
-      </c>
-      <c r="C77" s="82" t="inlineStr">
-        <is>
-          <t>Write the ontology in near-English sentences</t>
-        </is>
-      </c>
-      <c r="D77" s="82" t="inlineStr">
-        <is>
-          <t>'Every SensitiveSafeProduct is a Product that has-no restricted-ingredient.' It compiles to OWL.</t>
-        </is>
-      </c>
-      <c r="E77" s="83" t="inlineStr">
-        <is>
-          <t>cognitum.eu</t>
-        </is>
-      </c>
-      <c r="F77" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G77" s="85" t="inlineStr">
-        <is>
-          <t>Nice for explaining to a non-technical supervisor. Windows only, and small community.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="58" customHeight="1" s="49">
-      <c r="B78" s="86" t="inlineStr">
-        <is>
-          <t>Apache Jena Fuseki</t>
-        </is>
-      </c>
-      <c r="C78" s="87" t="inlineStr">
-        <is>
-          <t>Free triple store with a SPARQL endpoint</t>
-        </is>
-      </c>
-      <c r="D78" s="87" t="inlineStr">
-        <is>
-          <t>Store the graph, query it over HTTP. No editor, just the server.</t>
-        </is>
-      </c>
-      <c r="E78" s="88" t="inlineStr">
-        <is>
-          <t>jena.apache.org/documentation/fuseki2</t>
-        </is>
-      </c>
-      <c r="F78" s="89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G78" s="90" t="inlineStr">
-        <is>
-          <t>BIT-TECH 2025 USED THIS INSTEAD OF PROTEGE, with no editor at all. Its reasoning is weaker than GraphDB, but its SHACL engine is the fastest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="58" customHeight="1" s="49">
-      <c r="B79" s="81" t="inlineStr">
-        <is>
-          <t>R2RML / RML mapping files</t>
-        </is>
-      </c>
-      <c r="C79" s="82" t="inlineStr">
-        <is>
-          <t>The ontology is defined by the mapping, not by an editor</t>
-        </is>
-      </c>
-      <c r="D79" s="82" t="inlineStr">
-        <is>
-          <t>You never open an editor. The mapping file decides the shape of the graph.</t>
-        </is>
-      </c>
-      <c r="E79" s="83" t="inlineStr">
-        <is>
-          <t>rml.io</t>
-        </is>
-      </c>
-      <c r="F79" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G79" s="90" t="inlineStr">
-        <is>
-          <t>TOXIN KG 2025 WORKED THIS WAY. It is also how my pipeline works, so I should say so plainly: my ontology is built by a script, not by clicking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="26" customHeight="1" s="49">
-      <c r="B80" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REASONING AND RULES   (five ways to reason. See the 'Reasoning + SHACL' tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="58" customHeight="1" s="49">
-      <c r="B81" s="81" t="inlineStr">
-        <is>
-          <t>RDFS entailment</t>
-        </is>
-      </c>
-      <c r="C81" s="82" t="inlineStr">
-        <is>
-          <t>The cheapest reasoning. Subclass and domain/range only</t>
-        </is>
-      </c>
-      <c r="D81" s="82" t="inlineStr">
-        <is>
-          <t>If Cleanser is a subclass of Product, every cleanser becomes a product automatically.</t>
-        </is>
-      </c>
-      <c r="E81" s="83" t="inlineStr">
-        <is>
-          <t>w3.org/TR/rdf-mt</t>
-        </is>
-      </c>
-      <c r="F81" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G81" s="85" t="inlineStr">
-        <is>
-          <t>Free and always on in GraphDB. Does the hierarchy and nothing else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="58" customHeight="1" s="49">
-      <c r="B82" s="86" t="inlineStr">
-        <is>
-          <t>OWL 2 profiles (RL, EL, QL, DL)</t>
-        </is>
-      </c>
-      <c r="C82" s="87" t="inlineStr">
-        <is>
-          <t>Four cut-down versions of OWL that trade power for speed</t>
-        </is>
-      </c>
-      <c r="D82" s="87" t="inlineStr">
-        <is>
-          <t>RL runs as rules and scales. EL is for huge simple hierarchies. DL is full power but slow.</t>
-        </is>
-      </c>
-      <c r="E82" s="88" t="inlineStr">
-        <is>
-          <t>w3.org/TR/owl2-profiles</t>
-        </is>
-      </c>
-      <c r="F82" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G82" s="91" t="inlineStr">
-        <is>
-          <t>I should say in the chapter which profile I am in. My defined classes need DL. Saying 'OWL 2 DL' is a one-line answer to a very likely viva question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="58" customHeight="1" s="49">
-      <c r="B83" s="81" t="inlineStr">
-        <is>
-          <t>SHACL Core</t>
-        </is>
-      </c>
-      <c r="C83" s="82" t="inlineStr">
-        <is>
-          <t>Checks the data obeys rules, and names what broke</t>
-        </is>
-      </c>
-      <c r="D83" s="82" t="inlineStr">
-        <is>
-          <t>'Every product must have exactly one price.' It reports the exact product that has two.</t>
-        </is>
-      </c>
-      <c r="E83" s="83" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl</t>
-        </is>
-      </c>
-      <c r="F83" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G83" s="90" t="inlineStr">
-        <is>
-          <t>OWL cannot do this. OWL would decide the two prices are the same thing rather than complain. NOT ONE of my 28 papers uses SHACL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="58" customHeight="1" s="49">
-      <c r="B84" s="86" t="inlineStr">
-        <is>
-          <t>SHACL-AF  sh:TripleRule</t>
-        </is>
-      </c>
-      <c r="C84" s="87" t="inlineStr">
-        <is>
-          <t>A rule in the graph that adds a new triple</t>
-        </is>
-      </c>
-      <c r="D84" s="87" t="inlineStr">
-        <is>
-          <t>IF a product has 3 or more barrier lipids THEN it is a BarrierRepairProduct.</t>
-        </is>
-      </c>
-      <c r="E84" s="88" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl-af</t>
-        </is>
-      </c>
-      <c r="F84" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G84" s="91" t="inlineStr">
-        <is>
-          <t>Same result as a defined class but easier to read, and it can infer ANY triple. OWL can only ever infer types and sameAs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="58" customHeight="1" s="49">
-      <c r="B85" s="81" t="inlineStr">
-        <is>
-          <t>SHACL-AF  sh:SPARQLRule</t>
-        </is>
-      </c>
-      <c r="C85" s="82" t="inlineStr">
-        <is>
-          <t>A rule that runs a SPARQL CONSTRUCT and writes the answer back</t>
-        </is>
-      </c>
-      <c r="D85" s="82" t="inlineStr">
-        <is>
-          <t>Count how many EU-restricted ingredients a product has, store the number.</t>
-        </is>
-      </c>
-      <c r="E85" s="83" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl-af</t>
-        </is>
-      </c>
-      <c r="F85" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G85" s="85" t="inlineStr">
-        <is>
-          <t>OWL cannot count. This is the cleanest honest reason to bring SHACL in alongside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="58" customHeight="1" s="49">
-      <c r="B86" s="86" t="inlineStr">
-        <is>
-          <t>SHACL-SPARQL constraints</t>
-        </is>
-      </c>
-      <c r="C86" s="87" t="inlineStr">
-        <is>
-          <t>When the built-in checks are not enough, drop into SPARQL</t>
-        </is>
-      </c>
-      <c r="D86" s="87" t="inlineStr">
-        <is>
-          <t>'Every ingredient with an annex status must have an authority and a date.' My provenance rule, enforced by the machine.</t>
-        </is>
-      </c>
-      <c r="E86" s="88" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl</t>
-        </is>
-      </c>
-      <c r="F86" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G86" s="91" t="inlineStr">
-        <is>
-          <t>This is what turns my evidence-level design from a promise into something checkable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="58" customHeight="1" s="49">
-      <c r="B87" s="81" t="inlineStr">
-        <is>
-          <t>pySHACL</t>
-        </is>
-      </c>
-      <c r="C87" s="82" t="inlineStr">
-        <is>
-          <t>SHACL validator in Python</t>
-        </is>
-      </c>
-      <c r="D87" s="82" t="inlineStr">
-        <is>
-          <t>pip install pyshacl, then one command validates data against shapes.</t>
-        </is>
-      </c>
-      <c r="E87" s="83" t="inlineStr">
-        <is>
-          <t>github.com/RDFLib/pySHACL</t>
-        </is>
-      </c>
-      <c r="F87" s="92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G87" s="85" t="inlineStr">
-        <is>
-          <t>My pipeline is Python and it pairs with RDFLib. Slowest of the three engines but my graph is 1.8 million triples, which is nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="58" customHeight="1" s="49">
-      <c r="B88" s="86" t="inlineStr">
-        <is>
-          <t>Apache Jena SHACL</t>
-        </is>
-      </c>
-      <c r="C88" s="87" t="inlineStr">
-        <is>
-          <t>SHACL validator in Java, the fast one</t>
-        </is>
-      </c>
-      <c r="D88" s="87" t="inlineStr">
-        <is>
-          <t>Command line or library. Also reads SHACL-C, a compact syntax that is much easier to read than Turtle.</t>
-        </is>
-      </c>
-      <c r="E88" s="88" t="inlineStr">
-        <is>
-          <t>jena.apache.org/documentation/shacl</t>
-        </is>
-      </c>
-      <c r="F88" s="89" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G88" s="91" t="inlineStr">
-        <is>
-          <t>Benchmarked around 4x faster than pySHACL. Only matters if pySHACL gets slow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="58" customHeight="1" s="49">
-      <c r="B89" s="81" t="inlineStr">
-        <is>
-          <t>TopBraid SHACL API</t>
-        </is>
-      </c>
-      <c r="C89" s="82" t="inlineStr">
-        <is>
-          <t>The reference implementation</t>
-        </is>
-      </c>
-      <c r="D89" s="82" t="inlineStr">
-        <is>
-          <t>Java, on top of Jena. Defines what correct behaviour is when engines disagree.</t>
-        </is>
-      </c>
-      <c r="E89" s="83" t="inlineStr">
-        <is>
-          <t>github.com/TopQuadrant/shacl</t>
-        </is>
-      </c>
-      <c r="F89" s="84" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G89" s="85" t="inlineStr">
-        <is>
-          <t>Worth checking against if a validation result looks wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="58" customHeight="1" s="49">
-      <c r="B90" s="86" t="inlineStr">
-        <is>
-          <t>SPIN</t>
-        </is>
-      </c>
-      <c r="C90" s="87" t="inlineStr">
-        <is>
-          <t>The thing SHACL grew out of</t>
-        </is>
-      </c>
-      <c r="D90" s="87" t="inlineStr">
-        <is>
-          <t>SPARQL rules attached to classes. A TopQuadrant submission from 2011.</t>
-        </is>
-      </c>
-      <c r="E90" s="88" t="inlineStr">
-        <is>
-          <t>spinrdf.org</t>
-        </is>
-      </c>
-      <c r="F90" s="89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G90" s="91" t="inlineStr">
-        <is>
-          <t>Superseded by SHACL in 2017. Only useful to know because older papers mention it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="24" customHeight="1" s="49">
-      <c r="B92" s="154" t="inlineStr">
-        <is>
-          <t>Editors instead of Protege. My supervisor asked. Five of my 28 papers used no Protege at all.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="45" customHeight="1" s="49">
-      <c r="B93" s="155" t="inlineStr">
-        <is>
-          <t>WebProtege</t>
-        </is>
-      </c>
-      <c r="C93" s="156" t="inlineStr">
-        <is>
-          <t>Protege in a browser, multi-user</t>
-        </is>
-      </c>
-      <c r="D93" s="156" t="inlineStr">
-        <is>
-          <t>Same model as Protege but two people can edit at once, with change history and comments. Handles thousands of classes.</t>
-        </is>
-      </c>
-      <c r="E93" s="156" t="inlineStr">
-        <is>
-          <t>webprotege.stanford.edu</t>
-        </is>
-      </c>
-      <c r="F93" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G93" s="156" t="inlineStr">
-        <is>
-          <t>Useful if my supervisor wants to comment directly on the ontology instead of by email. Weaker than desktop Protege for reasoning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="58" customHeight="1" s="49">
-      <c r="B94" s="155" t="inlineStr">
-        <is>
-          <t>OntoRefine</t>
-        </is>
-      </c>
-      <c r="C94" s="156" t="inlineStr">
-        <is>
-          <t>Point-and-click CSV to RDF, inside GraphDB</t>
-        </is>
-      </c>
-      <c r="D94" s="156" t="inlineStr">
-        <is>
-          <t>You see your spreadsheet, you draw which column becomes a subject and which becomes a predicate, it writes the RDF.</t>
-        </is>
-      </c>
-      <c r="E94" s="156" t="inlineStr">
-        <is>
-          <t>graphdb.ontotext.com</t>
-        </is>
-      </c>
-      <c r="F94" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G94" s="156" t="inlineStr">
-        <is>
-          <t>Abesova used this instead of Protege. It works, but the mapping is trapped inside GraphDB. I cannot put it in an appendix or re-run it from a script. Morph-KGC does the same job as a file I can publish.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1" s="49">
-      <c r="B95" s="155" t="inlineStr">
-        <is>
-          <t>TopBraid Composer / EDG</t>
-        </is>
-      </c>
-      <c r="C95" s="156" t="inlineStr">
-        <is>
-          <t>The commercial editor, from the people who wrote SHACL</t>
-        </is>
-      </c>
-      <c r="D95" s="156" t="inlineStr">
-        <is>
-          <t>Full OWL editing plus the best SHACL support anywhere. EDG adds governance and workflows.</t>
-        </is>
-      </c>
-      <c r="E95" s="156" t="inlineStr">
-        <is>
-          <t>topquadrant.com</t>
-        </is>
-      </c>
-      <c r="F95" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G95" s="156" t="inlineStr">
-        <is>
-          <t>The reference implementation for SHACL, so worth knowing it exists. But commercial, and I do not need governance workflows for a one-person thesis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="45" customHeight="1" s="49">
-      <c r="B96" s="155" t="inlineStr">
-        <is>
-          <t>VocBench 3</t>
-        </is>
-      </c>
-      <c r="C96" s="156" t="inlineStr">
-        <is>
-          <t>Web platform for vocabularies and thesauri</t>
-        </is>
-      </c>
-      <c r="D96" s="156" t="inlineStr">
-        <is>
-          <t>Strong on SKOS, multilingual labels, and editorial workflow. Almost full OWL 2 coverage.</t>
-        </is>
-      </c>
-      <c r="E96" s="156" t="inlineStr">
-        <is>
-          <t>vocbench.uniroma2.it</t>
-        </is>
-      </c>
-      <c r="F96" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G96" s="156" t="inlineStr">
-        <is>
-          <t>Built for thesauri, not for defined classes. My benefits list is SKOS so it would suit that one part, but not the rest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="71" customHeight="1" s="49">
-      <c r="B97" s="155" t="inlineStr">
-        <is>
-          <t>ROBOT</t>
-        </is>
-      </c>
-      <c r="C97" s="156" t="inlineStr">
-        <is>
-          <t>A command-line tool for ontology jobs, from the OBO world</t>
-        </is>
-      </c>
-      <c r="D97" s="156" t="inlineStr">
-        <is>
-          <t>Convert formats, run a reasoner, extract a module, run quality reports. All from a script, no clicking.</t>
-        </is>
-      </c>
-      <c r="E97" s="156" t="inlineStr">
-        <is>
-          <t>github.com/ontodev/robot</t>
-        </is>
-      </c>
-      <c r="F97" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G97" s="156" t="inlineStr">
-        <is>
-          <t>This is how the serious biomedical ontologies are actually built. If I want my build to be repeatable rather than 'I clicked some things in Protege', this is the answer. Paper: Jackson et al., BMC Bioinformatics 2019.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="58" customHeight="1" s="49">
-      <c r="B98" s="155" t="inlineStr">
-        <is>
-          <t>LinkML</t>
-        </is>
-      </c>
-      <c r="C98" s="156" t="inlineStr">
-        <is>
-          <t>Write the model in YAML, generate everything else</t>
-        </is>
-      </c>
-      <c r="D98" s="156" t="inlineStr">
-        <is>
-          <t>One YAML schema generates OWL, SHACL, JSON Schema, Python classes and docs together.</t>
-        </is>
-      </c>
-      <c r="E98" s="156" t="inlineStr">
-        <is>
-          <t>linkml.io</t>
-        </is>
-      </c>
-      <c r="F98" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G98" s="156" t="inlineStr">
-        <is>
-          <t>Tempting, because it would give me OWL and SHACL from one source with no chance of them drifting apart. But it is another thing to learn and my ontology is small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="45" customHeight="1" s="49">
-      <c r="B99" s="155" t="inlineStr">
-        <is>
-          <t>Chowlk</t>
-        </is>
-      </c>
-      <c r="C99" s="156" t="inlineStr">
-        <is>
-          <t>Turn a diagram into OWL</t>
-        </is>
-      </c>
-      <c r="D99" s="156" t="inlineStr">
-        <is>
-          <t>You draw the ontology in diagrams.net using their notation, it outputs the OWL file.</t>
-        </is>
-      </c>
-      <c r="E99" s="156" t="inlineStr">
-        <is>
-          <t>chowlk.linkeddata.es</t>
-        </is>
-      </c>
-      <c r="F99" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G99" s="156" t="inlineStr">
-        <is>
-          <t>My chapter needs diagrams anyway. Drawing once and getting both the picture and the file is attractive. Same idea as CoModIDE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="32" customHeight="1" s="49">
-      <c r="B100" s="155" t="inlineStr">
-        <is>
-          <t>OWLGrEd</t>
-        </is>
-      </c>
-      <c r="C100" s="156" t="inlineStr">
-        <is>
-          <t>Draws an existing ontology as a UML-style picture</t>
-        </is>
-      </c>
-      <c r="D100" s="156" t="inlineStr">
-        <is>
-          <t>Point it at the OWL file, get a compact diagram of the whole thing.</t>
-        </is>
-      </c>
-      <c r="E100" s="156" t="inlineStr">
-        <is>
-          <t>owlgred.lumii.lv</t>
-        </is>
-      </c>
-      <c r="F100" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G100" s="156" t="inlineStr">
-        <is>
-          <t>Only for producing the figure in the chapter. Not for building.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="45" customHeight="1" s="49">
-      <c r="B101" s="155" t="inlineStr">
-        <is>
-          <t>Fluent Editor</t>
-        </is>
-      </c>
-      <c r="C101" s="156" t="inlineStr">
-        <is>
-          <t>Write the ontology in near-English sentences</t>
-        </is>
-      </c>
-      <c r="D101" s="156" t="inlineStr">
-        <is>
-          <t>'Every SensitiveSafeProduct is a Product that has-no restricted-ingredient.' It compiles to OWL.</t>
-        </is>
-      </c>
-      <c r="E101" s="156" t="inlineStr">
-        <is>
-          <t>cognitum.eu</t>
-        </is>
-      </c>
-      <c r="F101" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G101" s="156" t="inlineStr">
-        <is>
-          <t>Nice for explaining to a non-technical supervisor. Windows only, and small community.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="45" customHeight="1" s="49">
-      <c r="B102" s="155" t="inlineStr">
-        <is>
-          <t>Apache Jena Fuseki</t>
-        </is>
-      </c>
-      <c r="C102" s="156" t="inlineStr">
-        <is>
-          <t>Free triple store with a SPARQL endpoint</t>
-        </is>
-      </c>
-      <c r="D102" s="156" t="inlineStr">
-        <is>
-          <t>Store the graph, query it over HTTP. No editor, just the server.</t>
-        </is>
-      </c>
-      <c r="E102" s="156" t="inlineStr">
-        <is>
-          <t>jena.apache.org/documentation/fuseki2</t>
-        </is>
-      </c>
-      <c r="F102" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G102" s="156" t="inlineStr">
-        <is>
-          <t>bit-Tech 2025 used this instead of Protege, with no editor at all. Its reasoning is weaker than GraphDB, but its SHACL engine is the fastest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="45" customHeight="1" s="49">
-      <c r="B103" s="155" t="inlineStr">
-        <is>
-          <t>R2RML / RML mapping files</t>
-        </is>
-      </c>
-      <c r="C103" s="156" t="inlineStr">
-        <is>
-          <t>The ontology is defined by the mapping, not by an editor</t>
-        </is>
-      </c>
-      <c r="D103" s="156" t="inlineStr">
-        <is>
-          <t>You never open an editor. The mapping file decides the shape of the graph.</t>
-        </is>
-      </c>
-      <c r="E103" s="156" t="inlineStr">
-        <is>
-          <t>rml.io</t>
-        </is>
-      </c>
-      <c r="F103" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G103" s="156" t="inlineStr">
-        <is>
-          <t>TOXIN KG 2025 worked this way. It is also how my pipeline works, so I should say so plainly: my ontology is built by a script, not by clicking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="24" customHeight="1" s="49">
-      <c r="B104" s="154" t="inlineStr">
-        <is>
-          <t>Reasoning and rules. Five ways to reason. See the Reasoning + SHACL tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1" s="49">
-      <c r="B105" s="155" t="inlineStr">
-        <is>
-          <t>RDFS entailment</t>
-        </is>
-      </c>
-      <c r="C105" s="156" t="inlineStr">
-        <is>
-          <t>The cheapest reasoning. Subclass and domain/range only</t>
-        </is>
-      </c>
-      <c r="D105" s="156" t="inlineStr">
-        <is>
-          <t>If Cleanser is a subclass of Product, every cleanser becomes a product automatically.</t>
-        </is>
-      </c>
-      <c r="E105" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/rdf-mt</t>
-        </is>
-      </c>
-      <c r="F105" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G105" s="156" t="inlineStr">
-        <is>
-          <t>Free and always on in GraphDB. Does the hierarchy and nothing else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="45" customHeight="1" s="49">
-      <c r="B106" s="155" t="inlineStr">
-        <is>
-          <t>OWL 2 profiles (RL, EL, QL, DL)</t>
-        </is>
-      </c>
-      <c r="C106" s="156" t="inlineStr">
-        <is>
-          <t>Four cut-down versions of OWL that trade power for speed</t>
-        </is>
-      </c>
-      <c r="D106" s="156" t="inlineStr">
-        <is>
-          <t>RL runs as rules and scales. EL is for huge simple hierarchies. DL is full power but slow.</t>
-        </is>
-      </c>
-      <c r="E106" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/owl2-profiles</t>
-        </is>
-      </c>
-      <c r="F106" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G106" s="156" t="inlineStr">
-        <is>
-          <t>I should say in the chapter which profile I am in. My defined classes need DL. Saying 'OWL 2 DL' is a one-line answer to a very likely viva question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="45" customHeight="1" s="49">
-      <c r="B107" s="155" t="inlineStr">
-        <is>
-          <t>SHACL Core</t>
-        </is>
-      </c>
-      <c r="C107" s="156" t="inlineStr">
-        <is>
-          <t>Checks the data obeys rules, and names what broke</t>
-        </is>
-      </c>
-      <c r="D107" s="156" t="inlineStr">
-        <is>
-          <t>'Every product must have exactly one price.' It reports the exact product that has two.</t>
-        </is>
-      </c>
-      <c r="E107" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl</t>
-        </is>
-      </c>
-      <c r="F107" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G107" s="156" t="inlineStr">
-        <is>
-          <t>OWL cannot do this. OWL would decide the two prices are the same thing rather than complain. Not one of my 28 papers uses SHACL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="45" customHeight="1" s="49">
-      <c r="B108" s="155" t="inlineStr">
-        <is>
-          <t>SHACL-AF  sh:TripleRule</t>
-        </is>
-      </c>
-      <c r="C108" s="156" t="inlineStr">
-        <is>
-          <t>A rule in the graph that adds a new triple</t>
-        </is>
-      </c>
-      <c r="D108" s="156" t="inlineStr">
-        <is>
-          <t>If a product has three or more barrier lipids, it is a BarrierRepairProduct.</t>
-        </is>
-      </c>
-      <c r="E108" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl-af</t>
-        </is>
-      </c>
-      <c r="F108" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G108" s="156" t="inlineStr">
-        <is>
-          <t>Same result as a defined class but easier to read, and it can infer any triple. OWL can only ever infer types and sameAs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="32" customHeight="1" s="49">
-      <c r="B109" s="155" t="inlineStr">
-        <is>
-          <t>SHACL-AF  sh:SPARQLRule</t>
-        </is>
-      </c>
-      <c r="C109" s="156" t="inlineStr">
-        <is>
-          <t>A rule that runs a SPARQL CONSTRUCT and writes the answer back</t>
-        </is>
-      </c>
-      <c r="D109" s="156" t="inlineStr">
-        <is>
-          <t>Count how many EU-restricted ingredients a product has, store the number.</t>
-        </is>
-      </c>
-      <c r="E109" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl-af</t>
-        </is>
-      </c>
-      <c r="F109" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G109" s="156" t="inlineStr">
-        <is>
-          <t>OWL cannot count. This is the cleanest honest reason to bring SHACL in alongside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="45" customHeight="1" s="49">
-      <c r="B110" s="155" t="inlineStr">
-        <is>
-          <t>SHACL-SPARQL constraints</t>
-        </is>
-      </c>
-      <c r="C110" s="156" t="inlineStr">
-        <is>
-          <t>When the built-in checks are not enough, drop into SPARQL</t>
-        </is>
-      </c>
-      <c r="D110" s="156" t="inlineStr">
-        <is>
-          <t>'Every ingredient with an annex status must have an authority and a date.' My provenance rule, enforced by the machine.</t>
-        </is>
-      </c>
-      <c r="E110" s="156" t="inlineStr">
-        <is>
-          <t>w3.org/TR/shacl</t>
-        </is>
-      </c>
-      <c r="F110" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G110" s="156" t="inlineStr">
-        <is>
-          <t>This is what turns my evidence-level design from a promise into something checkable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="45" customHeight="1" s="49">
-      <c r="B111" s="155" t="inlineStr">
-        <is>
-          <t>pySHACL</t>
-        </is>
-      </c>
-      <c r="C111" s="156" t="inlineStr">
-        <is>
-          <t>SHACL validator in Python</t>
-        </is>
-      </c>
-      <c r="D111" s="156" t="inlineStr">
-        <is>
-          <t>pip install pyshacl, then one command validates data against shapes.</t>
-        </is>
-      </c>
-      <c r="E111" s="156" t="inlineStr">
-        <is>
-          <t>github.com/RDFLib/pySHACL</t>
-        </is>
-      </c>
-      <c r="F111" s="157" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G111" s="156" t="inlineStr">
-        <is>
-          <t>My pipeline is Python and it pairs with RDFLib. Slowest of the three engines but my graph is 1.8 million triples, which is nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="45" customHeight="1" s="49">
-      <c r="B112" s="155" t="inlineStr">
-        <is>
-          <t>Apache Jena SHACL</t>
-        </is>
-      </c>
-      <c r="C112" s="156" t="inlineStr">
-        <is>
-          <t>SHACL validator in Java, the fast one</t>
-        </is>
-      </c>
-      <c r="D112" s="156" t="inlineStr">
-        <is>
-          <t>Command line or library. Also reads SHACL-C, a compact syntax that is much easier to read than Turtle.</t>
-        </is>
-      </c>
-      <c r="E112" s="156" t="inlineStr">
-        <is>
-          <t>jena.apache.org/documentation/shacl</t>
-        </is>
-      </c>
-      <c r="F112" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G112" s="156" t="inlineStr">
-        <is>
-          <t>Benchmarked around four times faster than pySHACL. Only matters if pySHACL gets slow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="32" customHeight="1" s="49">
-      <c r="B113" s="155" t="inlineStr">
-        <is>
-          <t>TopBraid SHACL API</t>
-        </is>
-      </c>
-      <c r="C113" s="156" t="inlineStr">
-        <is>
-          <t>The reference implementation</t>
-        </is>
-      </c>
-      <c r="D113" s="156" t="inlineStr">
-        <is>
-          <t>Java, on top of Jena. Defines what correct behaviour is when engines disagree.</t>
-        </is>
-      </c>
-      <c r="E113" s="156" t="inlineStr">
-        <is>
-          <t>github.com/TopQuadrant/shacl</t>
-        </is>
-      </c>
-      <c r="F113" s="157" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
-      <c r="G113" s="156" t="inlineStr">
-        <is>
-          <t>Worth checking against if a validation result looks wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="32" customHeight="1" s="49">
-      <c r="B114" s="155" t="inlineStr">
-        <is>
-          <t>SPIN</t>
-        </is>
-      </c>
-      <c r="C114" s="156" t="inlineStr">
-        <is>
-          <t>The thing SHACL grew out of</t>
-        </is>
-      </c>
-      <c r="D114" s="156" t="inlineStr">
-        <is>
-          <t>SPARQL rules attached to classes. A TopQuadrant submission from 2011.</t>
-        </is>
-      </c>
-      <c r="E114" s="156" t="inlineStr">
-        <is>
-          <t>spinrdf.org</t>
-        </is>
-      </c>
-      <c r="F114" s="157" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G114" s="156" t="inlineStr">
-        <is>
-          <t>Superseded by SHACL in 2017. Only useful to know because older papers mention it.</t>
+      <c r="B86" s="159" t="inlineStr">
+        <is>
+          <t>Python desktop windows</t>
+        </is>
+      </c>
+      <c r="C86" s="159" t="inlineStr">
+        <is>
+          <t>Hansanie &amp; Silva</t>
+        </is>
+      </c>
+      <c r="D86" s="159" t="inlineStr">
+        <is>
+          <t>Built their desktop app with it</t>
+        </is>
+      </c>
+      <c r="E86" s="160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F86" s="159" t="inlineStr">
+        <is>
+          <t>I am not building a desktop app</t>
+        </is>
+      </c>
+      <c r="G86" s="161" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B20:G20"/>
+  <mergeCells count="11">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B104:G104"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B68:G68"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10784,14 +10457,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="49">
-      <c r="A1" s="158" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>The gap</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" s="49">
-      <c r="A2" s="159" t="inlineStr">
+      <c r="A2" s="155" t="inlineStr">
         <is>
           <t>One row per paper. Column 3 is what their work does not have. Columns 4 and 5 are mine: what I do instead, and what I still do not have.</t>
         </is>
@@ -10799,970 +10472,970 @@
     </row>
     <row r="3" ht="8" customHeight="1" s="49"/>
     <row r="4" ht="28" customHeight="1" s="49">
-      <c r="A4" s="160" t="inlineStr">
+      <c r="A4" s="156" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="160" t="inlineStr">
+      <c r="B4" s="156" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="C4" s="160" t="inlineStr">
+      <c r="C4" s="156" t="inlineStr">
         <is>
           <t>What they did</t>
         </is>
       </c>
-      <c r="D4" s="160" t="inlineStr">
+      <c r="D4" s="156" t="inlineStr">
         <is>
           <t>What is missing in it</t>
         </is>
       </c>
-      <c r="E4" s="160" t="inlineStr">
+      <c r="E4" s="156" t="inlineStr">
         <is>
           <t>What I do instead</t>
         </is>
       </c>
-      <c r="F4" s="160" t="inlineStr">
+      <c r="F4" s="156" t="inlineStr">
         <is>
           <t>What they have that I do not</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="49">
-      <c r="A5" s="154" t="inlineStr">
+      <c r="A5" s="157" t="inlineStr">
         <is>
           <t>Group A. Skincare and cosmetics ontologies. My direct competitors. The gap has to be stated against these seven.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="49">
-      <c r="A6" s="161" t="inlineStr">
+      <c r="A6" s="162" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="162" t="inlineStr">
+      <c r="B6" s="163" t="inlineStr">
         <is>
           <t>Moe &amp; Aung 2014</t>
         </is>
       </c>
-      <c r="C6" s="161" t="inlineStr">
+      <c r="C6" s="162" t="inlineStr">
         <is>
           <t>Two ontologies, one for cosmetics and one for skin problems. Six questions narrow you down, then a max-flow algorithm scores what is left.</t>
         </is>
       </c>
-      <c r="D6" s="161" t="inlineStr">
+      <c r="D6" s="162" t="inlineStr">
         <is>
           <t>No reasoner. No SPARQL. No outside data. They never say how many products. Nothing can be downloaded.</t>
         </is>
       </c>
-      <c r="E6" s="161" t="inlineStr">
+      <c r="E6" s="162" t="inlineStr">
         <is>
           <t>12,629 real products with real prices. A reasoner that runs. Every ingredient tied to the EU database.</t>
         </is>
       </c>
-      <c r="F6" s="161" t="inlineStr">
+      <c r="F6" s="162" t="inlineStr">
         <is>
           <t>Their question-and-eliminate interaction is better than anything I have. I only have queries.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="49">
-      <c r="A7" s="161" t="inlineStr">
+      <c r="A7" s="162" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="162" t="inlineStr">
+      <c r="B7" s="163" t="inlineStr">
         <is>
           <t>OntoCosmetic 2021/23</t>
         </is>
       </c>
-      <c r="C7" s="161" t="inlineStr">
+      <c r="C7" s="162" t="inlineStr">
         <is>
           <t>Helps a chemist formulate a cream. SWRL rules with a high and a low threshold per ingredient function. Published and downloadable.</t>
         </is>
       </c>
-      <c r="D7" s="161" t="inlineStr">
+      <c r="D7" s="162" t="inlineStr">
         <is>
           <t>It is for the person making the product, not the person buying it. No shopper, no price, no availability, no skin type.</t>
         </is>
       </c>
-      <c r="E7" s="161" t="inlineStr">
+      <c r="E7" s="162" t="inlineStr">
         <is>
           <t>The same chemistry idea, pointed at the buyer. Their rule shape is what I copy for my defined classes.</t>
         </is>
       </c>
-      <c r="F7" s="161" t="inlineStr">
+      <c r="F7" s="162" t="inlineStr">
         <is>
           <t>They publish their OWL file at a permanent address and I have not. They also ran user testing across iterations.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="49">
-      <c r="A8" s="161" t="inlineStr">
+      <c r="A8" s="162" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="162" t="inlineStr">
+      <c r="B8" s="163" t="inlineStr">
         <is>
           <t>Hansanie &amp; Silva 2024</t>
         </is>
       </c>
-      <c r="C8" s="161" t="inlineStr">
+      <c r="C8" s="162" t="inlineStr">
         <is>
           <t>A photo goes into a small CNN, the grade comes out, the ontology picks products. Pellet checks consistency.</t>
         </is>
       </c>
-      <c r="D8" s="161" t="inlineStr">
+      <c r="D8" s="162" t="inlineStr">
         <is>
           <t>The ontology is small and never released. No SPARQL, no outside data. The CNN does the work and the ontology is decoration.</t>
         </is>
       </c>
-      <c r="E8" s="161" t="inlineStr">
+      <c r="E8" s="162" t="inlineStr">
         <is>
           <t>No photos. The reasoning is the contribution, not an add-on. My ingredient layer is the part theirs does not have.</t>
         </is>
       </c>
-      <c r="F8" s="161" t="inlineStr">
+      <c r="F8" s="162" t="inlineStr">
         <is>
           <t>They have a working app with an interface, and 24 people tested it. I have no interface.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1" s="49">
-      <c r="A9" s="161" t="inlineStr">
+      <c r="A9" s="162" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="162" t="inlineStr">
+      <c r="B9" s="163" t="inlineStr">
         <is>
           <t>Abesova 2023 (VU)</t>
         </is>
       </c>
-      <c r="C9" s="161" t="inlineStr">
+      <c r="C9" s="162" t="inlineStr">
         <is>
           <t>Student project. Sephora review CSV to RDF with OntoRefine, GraphDB, defined classes like 'OilyScore = 5', then SPARQL picks 9 products.</t>
         </is>
       </c>
-      <c r="D9" s="161" t="inlineStr">
+      <c r="D9" s="162" t="inlineStr">
         <is>
           <t>Not peer reviewed. It recommends from review scores only and never looks inside the product. They admit one property was implemented wrong.</t>
         </is>
       </c>
-      <c r="E9" s="161" t="inlineStr">
+      <c r="E9" s="162" t="inlineStr">
         <is>
           <t>The same defined-class method, but driven by ingredients instead of star ratings. That is their third limitation.</t>
         </is>
       </c>
-      <c r="F9" s="161" t="inlineStr">
+      <c r="F9" s="162" t="inlineStr">
         <is>
           <t>They link to DBpedia for a live map, and they have a working country-to-shop link. My Lebanon layer does that for one country.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1" s="49">
-      <c r="A10" s="161" t="inlineStr">
+      <c r="A10" s="162" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="162" t="inlineStr">
+      <c r="B10" s="163" t="inlineStr">
         <is>
           <t>bit-Tech 2025</t>
         </is>
       </c>
-      <c r="C10" s="161" t="inlineStr">
+      <c r="C10" s="162" t="inlineStr">
         <is>
           <t>METHONTOLOGY, Apache Jena Fuseki, SPARQL with reasoning, about 3,800 products. My closest competitor on paper.</t>
         </is>
       </c>
-      <c r="D10" s="161" t="inlineStr">
+      <c r="D10" s="162" t="inlineStr">
         <is>
           <t>I only have the abstract. No ingredients, no regulation link, no provenance mentioned.</t>
         </is>
       </c>
-      <c r="E10" s="161" t="inlineStr">
+      <c r="E10" s="162" t="inlineStr">
         <is>
           <t>Ingredients tied to EU law, four levels of evidence, and real shop availability. None of which they claim.</t>
         </is>
       </c>
-      <c r="F10" s="161" t="inlineStr">
+      <c r="F10" s="162" t="inlineStr">
         <is>
           <t>3,800 products, in a published venue, with a named method, already finished. I need the full PDF before I can say more.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" s="49">
-      <c r="A11" s="161" t="inlineStr">
+      <c r="A11" s="162" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="162" t="inlineStr">
+      <c r="B11" s="163" t="inlineStr">
         <is>
           <t>Utari 2023</t>
         </is>
       </c>
-      <c r="C11" s="161" t="inlineStr">
+      <c r="C11" s="162" t="inlineStr">
         <is>
           <t>METHONTOLOGY on 62 products, evaluated with SPARQL queries.</t>
         </is>
       </c>
-      <c r="D11" s="161" t="inlineStr">
+      <c r="D11" s="162" t="inlineStr">
         <is>
           <t>62 products is a demonstration, not a system. No tools stated. Nothing downloadable.</t>
         </is>
       </c>
-      <c r="E11" s="161" t="inlineStr">
+      <c r="E11" s="162" t="inlineStr">
         <is>
           <t>12,629 products, and every one has a source and a date.</t>
         </is>
       </c>
-      <c r="F11" s="161" t="inlineStr">
+      <c r="F11" s="162" t="inlineStr">
         <is>
           <t>Nothing I can see.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1" s="49">
-      <c r="A12" s="161" t="inlineStr">
+      <c r="A12" s="162" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="162" t="inlineStr">
+      <c r="B12" s="163" t="inlineStr">
         <is>
           <t>Mahadewi 2024</t>
         </is>
       </c>
-      <c r="C12" s="161" t="inlineStr">
+      <c r="C12" s="162" t="inlineStr">
         <is>
           <t>Slope One collaborative filtering, measured with SUS and MAE.</t>
         </is>
       </c>
-      <c r="D12" s="161" t="inlineStr">
+      <c r="D12" s="162" t="inlineStr">
         <is>
           <t>Not an ontology. It needs a ratings matrix, and it cannot explain why it recommended anything.</t>
         </is>
       </c>
-      <c r="E12" s="161" t="inlineStr">
+      <c r="E12" s="162" t="inlineStr">
         <is>
           <t>Reasoning that can show its working. Cold start is not a problem for me.</t>
         </is>
       </c>
-      <c r="F12" s="161" t="inlineStr">
+      <c r="F12" s="162" t="inlineStr">
         <is>
           <t>Two named evaluation instruments and real numbers. My evaluation is still on paper.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="49">
-      <c r="A13" s="154" t="inlineStr">
+      <c r="A13" s="157" t="inlineStr">
         <is>
           <t>Group B. Ingredients, regulation and skin conditions. Not recommenders. These give my ingredient and concern layers a standing nobody in group A has.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1" s="49">
-      <c r="A14" s="161" t="inlineStr">
+      <c r="A14" s="162" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B14" s="162" t="inlineStr">
+      <c r="B14" s="163" t="inlineStr">
         <is>
           <t>TOXIN KG 2025</t>
         </is>
       </c>
-      <c r="C14" s="161" t="inlineStr">
+      <c r="C14" s="162" t="inlineStr">
         <is>
           <t>A toxicology graph. R2RML from spreadsheets, TXPO as the ontology, named graphs so every fact keeps its source.</t>
         </is>
       </c>
-      <c r="D14" s="161" t="inlineStr">
+      <c r="D14" s="162" t="inlineStr">
         <is>
           <t>Toxicology, not cosmetics. No consumer anywhere in it.</t>
         </is>
       </c>
-      <c r="E14" s="161" t="inlineStr">
+      <c r="E14" s="162" t="inlineStr">
         <is>
           <t>I take the named-graph idea. One graph per source: Skinsort, Amazon, the six Lebanese shops.</t>
         </is>
       </c>
-      <c r="F14" s="161" t="inlineStr">
+      <c r="F14" s="162" t="inlineStr">
         <is>
           <t>Their provenance is further along than mine, and they score study reliability automatically.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1" s="49">
-      <c r="A15" s="161" t="inlineStr">
+      <c r="A15" s="162" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B15" s="162" t="inlineStr">
+      <c r="B15" s="163" t="inlineStr">
         <is>
           <t>HaCKG 2025</t>
         </is>
       </c>
-      <c r="C15" s="161" t="inlineStr">
+      <c r="C15" s="162" t="inlineStr">
         <is>
           <t>A neural graph network that predicts halal status from a knowledge graph.</t>
         </is>
       </c>
-      <c r="D15" s="161" t="inlineStr">
+      <c r="D15" s="162" t="inlineStr">
         <is>
           <t>The reasoning sits inside a neural net, so it cannot explain itself. No rules.</t>
         </is>
       </c>
-      <c r="E15" s="161" t="inlineStr">
+      <c r="E15" s="162" t="inlineStr">
         <is>
           <t>Rules I can print. Anyone can check a single decision by hand.</t>
         </is>
       </c>
-      <c r="F15" s="161" t="inlineStr">
+      <c r="F15" s="162" t="inlineStr">
         <is>
           <t>It beats rule systems on accuracy, and it handles cases no rule covers.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1" s="49">
-      <c r="A16" s="161" t="inlineStr">
+      <c r="A16" s="162" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B16" s="162" t="inlineStr">
+      <c r="B16" s="163" t="inlineStr">
         <is>
           <t>CosIng-KG</t>
         </is>
       </c>
-      <c r="C16" s="161" t="inlineStr">
+      <c r="C16" s="162" t="inlineStr">
         <is>
           <t>CosIng already turned into RDF and published on GitHub.</t>
         </is>
       </c>
-      <c r="D16" s="161" t="inlineStr">
+      <c r="D16" s="162" t="inlineStr">
         <is>
           <t>Not a paper, and I have not checked yet whether it works.</t>
         </is>
       </c>
-      <c r="E16" s="161" t="inlineStr">
+      <c r="E16" s="162" t="inlineStr">
         <is>
           <t>If it is usable I reuse it and save weeks. If not, I build the ingredient layer myself.</t>
         </is>
       </c>
-      <c r="F16" s="161" t="inlineStr">
+      <c r="F16" s="162" t="inlineStr">
         <is>
           <t>It may already hold a cleaner version of my whole ingredient layer.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" s="49">
-      <c r="A17" s="161" t="inlineStr">
+      <c r="A17" s="162" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="162" t="inlineStr">
+      <c r="B17" s="163" t="inlineStr">
         <is>
           <t>CCIBP 2023</t>
         </is>
       </c>
-      <c r="C17" s="161" t="inlineStr">
+      <c r="C17" s="162" t="inlineStr">
         <is>
           <t>A chemical and biological database of cosmetic ingredients.</t>
         </is>
       </c>
-      <c r="D17" s="161" t="inlineStr">
+      <c r="D17" s="162" t="inlineStr">
         <is>
           <t>A resource, not a system. No recommendation, no consumer.</t>
         </is>
       </c>
-      <c r="E17" s="161" t="inlineStr">
+      <c r="E17" s="162" t="inlineStr">
         <is>
           <t>I use it to cross-check my ingredient names.</t>
         </is>
       </c>
-      <c r="F17" s="161" t="inlineStr">
+      <c r="F17" s="162" t="inlineStr">
         <is>
           <t>Chemoinformatics depth I do not have.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" s="49">
-      <c r="A18" s="161" t="inlineStr">
+      <c r="A18" s="162" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B18" s="162" t="inlineStr">
+      <c r="B18" s="163" t="inlineStr">
         <is>
           <t>DermO 2016</t>
         </is>
       </c>
-      <c r="C18" s="161" t="inlineStr">
+      <c r="C18" s="162" t="inlineStr">
         <is>
           <t>3,000 skin disease terms written by dermatologists, on BioPortal.</t>
         </is>
       </c>
-      <c r="D18" s="161" t="inlineStr">
+      <c r="D18" s="162" t="inlineStr">
         <is>
           <t>A terminology. It does not recommend anything.</t>
         </is>
       </c>
-      <c r="E18" s="161" t="inlineStr">
+      <c r="E18" s="162" t="inlineStr">
         <is>
           <t>I align my six concern values to it. Six lines of code, and my medical claims stop being my own invention.</t>
         </is>
       </c>
-      <c r="F18" s="161" t="inlineStr">
+      <c r="F18" s="162" t="inlineStr">
         <is>
           <t>Clinical authority. Mine is borrowed from them.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" s="49">
-      <c r="A19" s="161" t="inlineStr">
+      <c r="A19" s="162" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B19" s="162" t="inlineStr">
+      <c r="B19" s="163" t="inlineStr">
         <is>
           <t>Halal flavouring 2024</t>
         </is>
       </c>
-      <c r="C19" s="161" t="inlineStr">
+      <c r="C19" s="162" t="inlineStr">
         <is>
           <t>Ingredient to status to authority, with the certifying body as a real entity in the graph.</t>
         </is>
       </c>
-      <c r="D19" s="161" t="inlineStr">
+      <c r="D19" s="162" t="inlineStr">
         <is>
           <t>Food, not cosmetics.</t>
         </is>
       </c>
-      <c r="E19" s="161" t="inlineStr">
+      <c r="E19" s="162" t="inlineStr">
         <is>
           <t>I copy that three-part shape for CosIng annex status and for evidence levels.</t>
         </is>
       </c>
-      <c r="F19" s="161" t="inlineStr">
+      <c r="F19" s="162" t="inlineStr">
         <is>
           <t>They consulted the certifying body. I have consulted nobody.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" s="49">
-      <c r="A20" s="161" t="inlineStr">
+      <c r="A20" s="162" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B20" s="162" t="inlineStr">
+      <c r="B20" s="163" t="inlineStr">
         <is>
           <t>Klaschka 2015</t>
         </is>
       </c>
-      <c r="C20" s="161" t="inlineStr">
+      <c r="C20" s="162" t="inlineStr">
         <is>
           <t>Counts how many cosmetic ingredients carry hazard classifications under REACH and CLP.</t>
         </is>
       </c>
-      <c r="D20" s="161" t="inlineStr">
+      <c r="D20" s="162" t="inlineStr">
         <is>
           <t>An analysis, not a tool.</t>
         </is>
       </c>
-      <c r="E20" s="161" t="inlineStr">
+      <c r="E20" s="162" t="inlineStr">
         <is>
           <t>It gives me the sentence that justifies why a regulation link matters at all.</t>
         </is>
       </c>
-      <c r="F20" s="161" t="inlineStr">
+      <c r="F20" s="162" t="inlineStr">
         <is>
           <t>Nothing structural.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" s="49">
-      <c r="A21" s="161" t="inlineStr">
+      <c r="A21" s="162" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="162" t="inlineStr">
+      <c r="B21" s="163" t="inlineStr">
         <is>
           <t>MVFM 2026</t>
         </is>
       </c>
-      <c r="C21" s="161" t="inlineStr">
+      <c r="C21" s="162" t="inlineStr">
         <is>
           <t>A framework tested on three products by hand.</t>
         </is>
       </c>
-      <c r="D21" s="161" t="inlineStr">
+      <c r="D21" s="162" t="inlineStr">
         <is>
           <t>Three products. No tools, no ontology file.</t>
         </is>
       </c>
-      <c r="E21" s="161" t="inlineStr">
+      <c r="E21" s="162" t="inlineStr">
         <is>
           <t>Scale, and everything automated.</t>
         </is>
       </c>
-      <c r="F21" s="161" t="inlineStr">
+      <c r="F21" s="162" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="49">
-      <c r="A22" s="154" t="inlineStr">
+      <c r="A22" s="157" t="inlineStr">
         <is>
           <t>Group C. Ontology recommenders in other fields. Nobody solved my problems in skincare. People solved them in food and shopping.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1" s="49">
-      <c r="A23" s="161" t="inlineStr">
+      <c r="A23" s="162" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B23" s="162" t="inlineStr">
+      <c r="B23" s="163" t="inlineStr">
         <is>
           <t>Middleton 2004</t>
         </is>
       </c>
-      <c r="C23" s="161" t="inlineStr">
+      <c r="C23" s="162" t="inlineStr">
         <is>
           <t>The paper that shows an ontology in a recommender is a reasonable choice. ACM TOIS, thousands of citations.</t>
         </is>
       </c>
-      <c r="D23" s="161" t="inlineStr">
+      <c r="D23" s="162" t="inlineStr">
         <is>
           <t>Academic papers, not products. It predates SPARQL.</t>
         </is>
       </c>
-      <c r="E23" s="161" t="inlineStr">
+      <c r="E23" s="162" t="inlineStr">
         <is>
           <t>I cite it first in the chapter. Its cold-start argument is my cold-start argument.</t>
         </is>
       </c>
-      <c r="F23" s="161" t="inlineStr">
+      <c r="F23" s="162" t="inlineStr">
         <is>
           <t>Real deployments with real users over years. Mine is a dataset.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1" s="49">
-      <c r="A24" s="161" t="inlineStr">
+      <c r="A24" s="162" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="162" t="inlineStr">
+      <c r="B24" s="163" t="inlineStr">
         <is>
           <t>FoodKG 2019/21</t>
         </is>
       </c>
-      <c r="C24" s="161" t="inlineStr">
+      <c r="C24" s="162" t="inlineStr">
         <is>
           <t>Recipes, ingredients, nutrition from an authority, allergies as hard constraints. A SPARQL service on top. Published.</t>
         </is>
       </c>
-      <c r="D24" s="161" t="inlineStr">
+      <c r="D24" s="162" t="inlineStr">
         <is>
           <t>Food. And they have no regulator the way I have CosIng.</t>
         </is>
       </c>
-      <c r="E24" s="161" t="inlineStr">
+      <c r="E24" s="162" t="inlineStr">
         <is>
           <t>Almost the same shape as mine. Recipes are products, nutrition data is CosIng, allergies are the EU allergen list.</t>
         </is>
       </c>
-      <c r="F24" s="161" t="inlineStr">
+      <c r="F24" s="162" t="inlineStr">
         <is>
           <t>Nearly everything. They publish, they state a maintenance plan, and they built several applications on one graph. This is my model.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1" s="49">
-      <c r="A25" s="161" t="inlineStr">
+      <c r="A25" s="162" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B25" s="162" t="inlineStr">
+      <c r="B25" s="163" t="inlineStr">
         <is>
           <t>Di Noia / Ostuni</t>
         </is>
       </c>
-      <c r="C25" s="161" t="inlineStr">
+      <c r="C25" s="162" t="inlineStr">
         <is>
           <t>Similarity computed from links in the graph, not from words. No ratings needed.</t>
         </is>
       </c>
-      <c r="D25" s="161" t="inlineStr">
+      <c r="D25" s="162" t="inlineStr">
         <is>
           <t>Movies. And they say entity matching is the hard part.</t>
         </is>
       </c>
-      <c r="E25" s="161" t="inlineStr">
+      <c r="E25" s="162" t="inlineStr">
         <is>
           <t>I can compute product similarity with no user history, which is my situation.</t>
         </is>
       </c>
-      <c r="F25" s="161" t="inlineStr">
+      <c r="F25" s="162" t="inlineStr">
         <is>
           <t>Offline benchmarks against baselines.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1" s="49">
-      <c r="A26" s="161" t="inlineStr">
+      <c r="A26" s="162" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="162" t="inlineStr">
+      <c r="B26" s="163" t="inlineStr">
         <is>
           <t>AliCoCo 2020</t>
         </is>
       </c>
-      <c r="C26" s="161" t="inlineStr">
+      <c r="C26" s="162" t="inlineStr">
         <is>
           <t>Alibaba's own concept net, running at real scale.</t>
         </is>
       </c>
-      <c r="D26" s="161" t="inlineStr">
+      <c r="D26" s="162" t="inlineStr">
         <is>
           <t>Internal, closed, and very large. Nothing reusable.</t>
         </is>
       </c>
-      <c r="E26" s="161" t="inlineStr">
+      <c r="E26" s="162" t="inlineStr">
         <is>
           <t>I work at a size one person can check.</t>
         </is>
       </c>
-      <c r="F26" s="161" t="inlineStr">
+      <c r="F26" s="162" t="inlineStr">
         <is>
           <t>Online metrics from millions of users.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1" s="49">
-      <c r="A27" s="161" t="inlineStr">
+      <c r="A27" s="162" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B27" s="162" t="inlineStr">
+      <c r="B27" s="163" t="inlineStr">
         <is>
           <t>Guo survey 2022</t>
         </is>
       </c>
-      <c r="C27" s="161" t="inlineStr">
+      <c r="C27" s="162" t="inlineStr">
         <is>
           <t>Surveys knowledge-graph recommenders and sorts them into families.</t>
         </is>
       </c>
-      <c r="D27" s="161" t="inlineStr">
+      <c r="D27" s="162" t="inlineStr">
         <is>
           <t>A survey. Nothing built.</t>
         </is>
       </c>
-      <c r="E27" s="161" t="inlineStr">
+      <c r="E27" s="162" t="inlineStr">
         <is>
           <t>It tells me which family I am in, so I can name it in the chapter.</t>
         </is>
       </c>
-      <c r="F27" s="161" t="inlineStr">
+      <c r="F27" s="162" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1" s="49">
-      <c r="A28" s="161" t="inlineStr">
+      <c r="A28" s="162" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B28" s="162" t="inlineStr">
+      <c r="B28" s="163" t="inlineStr">
         <is>
           <t>E-Prod 2023</t>
         </is>
       </c>
-      <c r="C28" s="161" t="inlineStr">
+      <c r="C28" s="162" t="inlineStr">
         <is>
           <t>Machine learning plus semantic matching, tested on 250+ real users against collaborative filtering.</t>
         </is>
       </c>
-      <c r="D28" s="161" t="inlineStr">
+      <c r="D28" s="162" t="inlineStr">
         <is>
           <t>General e-commerce. No regulation, no chemistry.</t>
         </is>
       </c>
-      <c r="E28" s="161" t="inlineStr">
+      <c r="E28" s="162" t="inlineStr">
         <is>
           <t>My matching is over ingredients, with a legal backing.</t>
         </is>
       </c>
-      <c r="F28" s="161" t="inlineStr">
+      <c r="F28" s="162" t="inlineStr">
         <is>
           <t>250 real users. That is a proper evaluation and I do not have one.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1" s="49">
-      <c r="A29" s="161" t="inlineStr">
+      <c r="A29" s="162" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B29" s="162" t="inlineStr">
+      <c r="B29" s="163" t="inlineStr">
         <is>
           <t>Lahoud 2022</t>
         </is>
       </c>
-      <c r="C29" s="161" t="inlineStr">
+      <c r="C29" s="162" t="inlineStr">
         <is>
           <t>Ontology plus case-based reasoning, evaluated on Lebanese students.</t>
         </is>
       </c>
-      <c r="D29" s="161" t="inlineStr">
+      <c r="D29" s="162" t="inlineStr">
         <is>
           <t>Not skincare.</t>
         </is>
       </c>
-      <c r="E29" s="161" t="inlineStr">
+      <c r="E29" s="162" t="inlineStr">
         <is>
           <t>Proof that this kind of work gets done and published in Lebanon.</t>
         </is>
       </c>
-      <c r="F29" s="161" t="inlineStr">
+      <c r="F29" s="162" t="inlineStr">
         <is>
           <t>A comparative evaluation with real local users.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="49">
-      <c r="A30" s="154" t="inlineStr">
+      <c r="A30" s="157" t="inlineStr">
         <is>
           <t>Group D. Evaluation, and the alternative I have to answer. What counts as good, and the deep learning answer to the same problem.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1" s="49">
-      <c r="A31" s="161" t="inlineStr">
+      <c r="A31" s="162" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B31" s="162" t="inlineStr">
+      <c r="B31" s="163" t="inlineStr">
         <is>
           <t>Rahayu review 2022</t>
         </is>
       </c>
-      <c r="C31" s="161" t="inlineStr">
+      <c r="C31" s="162" t="inlineStr">
         <is>
           <t>Reviews 28 ontology-based recommender studies.</t>
         </is>
       </c>
-      <c r="D31" s="161" t="inlineStr">
+      <c r="D31" s="162" t="inlineStr">
         <is>
           <t>A review.</t>
         </is>
       </c>
-      <c r="E31" s="161" t="inlineStr">
+      <c r="E31" s="162" t="inlineStr">
         <is>
           <t>Its finding is my justification. Not one of the 28 described how it was evaluated. So I describe mine.</t>
         </is>
       </c>
-      <c r="F31" s="161" t="inlineStr">
+      <c r="F31" s="162" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1" s="49">
-      <c r="A32" s="161" t="inlineStr">
+      <c r="A32" s="162" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B32" s="162" t="inlineStr">
+      <c r="B32" s="163" t="inlineStr">
         <is>
           <t>Tarus 2017</t>
         </is>
       </c>
-      <c r="C32" s="161" t="inlineStr">
+      <c r="C32" s="162" t="inlineStr">
         <is>
           <t>Ontology plus sequential pattern mining for e-learning.</t>
         </is>
       </c>
-      <c r="D32" s="161" t="inlineStr">
+      <c r="D32" s="162" t="inlineStr">
         <is>
           <t>E-learning.</t>
         </is>
       </c>
-      <c r="E32" s="161" t="inlineStr">
+      <c r="E32" s="162" t="inlineStr">
         <is>
           <t>The idea that order matters. My routine_step column is the same instinct.</t>
         </is>
       </c>
-      <c r="F32" s="161" t="inlineStr">
+      <c r="F32" s="162" t="inlineStr">
         <is>
           <t>Experiments against baselines.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1" s="49">
-      <c r="A33" s="161" t="inlineStr">
+      <c r="A33" s="162" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B33" s="162" t="inlineStr">
+      <c r="B33" s="163" t="inlineStr">
         <is>
           <t>COPPER 2025</t>
         </is>
       </c>
-      <c r="C33" s="161" t="inlineStr">
+      <c r="C33" s="162" t="inlineStr">
         <is>
           <t>Evaluated on three layers: the process against OBO principles, logical consistency, then competency questions.</t>
         </is>
       </c>
-      <c r="D33" s="161" t="inlineStr">
+      <c r="D33" s="162" t="inlineStr">
         <is>
           <t>Not skincare.</t>
         </is>
       </c>
-      <c r="E33" s="161" t="inlineStr">
+      <c r="E33" s="162" t="inlineStr">
         <is>
           <t>This is the evaluation design I copy. It is the most complete one in my review.</t>
         </is>
       </c>
-      <c r="F33" s="161" t="inlineStr">
+      <c r="F33" s="162" t="inlineStr">
         <is>
           <t>They ran it. I have only planned it.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1" s="49">
-      <c r="A34" s="161" t="inlineStr">
+      <c r="A34" s="162" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B34" s="162" t="inlineStr">
+      <c r="B34" s="163" t="inlineStr">
         <is>
           <t>FEVR 2022</t>
         </is>
       </c>
-      <c r="C34" s="161" t="inlineStr">
+      <c r="C34" s="162" t="inlineStr">
         <is>
           <t>A framework for how ontology recommenders should be evaluated.</t>
         </is>
       </c>
-      <c r="D34" s="161" t="inlineStr">
+      <c r="D34" s="162" t="inlineStr">
         <is>
           <t>A framework.</t>
         </is>
       </c>
-      <c r="E34" s="161" t="inlineStr">
+      <c r="E34" s="162" t="inlineStr">
         <is>
           <t>It tells me to match the evaluation to the goal, instead of reporting precision by reflex.</t>
         </is>
       </c>
-      <c r="F34" s="161" t="inlineStr">
+      <c r="F34" s="162" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1" s="49">
-      <c r="A35" s="161" t="inlineStr">
+      <c r="A35" s="162" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B35" s="162" t="inlineStr">
+      <c r="B35" s="163" t="inlineStr">
         <is>
           <t>Lee 2024 (lululab)</t>
         </is>
       </c>
-      <c r="C35" s="161" t="inlineStr">
+      <c r="C35" s="162" t="inlineStr">
         <is>
           <t>A deep neural network plus AI skin analysis. No ontology.</t>
         </is>
       </c>
-      <c r="D35" s="161" t="inlineStr">
+      <c r="D35" s="162" t="inlineStr">
         <is>
           <t>It cannot explain a single recommendation. No ingredients, no rules, no regulation.</t>
         </is>
       </c>
-      <c r="E35" s="161" t="inlineStr">
+      <c r="E35" s="162" t="inlineStr">
         <is>
           <t>Everything I do can be inspected. That is the argument.</t>
         </is>
       </c>
-      <c r="F35" s="161" t="inlineStr">
+      <c r="F35" s="162" t="inlineStr">
         <is>
           <t>It works today, at commercial scale, with real customers.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1" s="49">
-      <c r="A36" s="161" t="inlineStr">
+      <c r="A36" s="162" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B36" s="162" t="inlineStr">
+      <c r="B36" s="163" t="inlineStr">
         <is>
           <t>Ali 2026</t>
         </is>
       </c>
-      <c r="C36" s="161" t="inlineStr">
+      <c r="C36" s="162" t="inlineStr">
         <is>
           <t>An ontology-grounded graph feeding an LLM. Three conditions, the same 60 questions.</t>
         </is>
       </c>
-      <c r="D36" s="161" t="inlineStr">
+      <c r="D36" s="162" t="inlineStr">
         <is>
           <t>Very new. Not skincare.</t>
         </is>
       </c>
-      <c r="E36" s="161" t="inlineStr">
+      <c r="E36" s="162" t="inlineStr">
         <is>
           <t>It shows the ontology stops the model inventing things. This is my future work chapter.</t>
         </is>
       </c>
-      <c r="F36" s="161" t="inlineStr">
+      <c r="F36" s="162" t="inlineStr">
         <is>
           <t>A clean experimental design I should copy.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" s="49">
-      <c r="A38" s="154" t="inlineStr">
+      <c r="A38" s="157" t="inlineStr">
         <is>
           <t>The gap in one sentence</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1" s="49">
-      <c r="A39" s="163" t="inlineStr">
+      <c r="A39" s="164" t="inlineStr">
         <is>
           <t>Everyone recommends from ratings, reviews or photos. Nobody recommends from what is in the product, tied to the regulator, with a record of where each fact came from, for products you can really buy.
 Abesova's third limitation says this in their own words: "class restrictions based on ingredients could be developed. This would ensure a more symbolic and chemical approach, compared to the statistical one that is currently employed."</t>
@@ -11802,14 +11475,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="49">
-      <c r="A1" s="158" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>Reasoning, and where SHACL fits</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" s="49">
-      <c r="A2" s="159" t="inlineStr">
+      <c r="A2" s="155" t="inlineStr">
         <is>
           <t>Reasoning means the machine works something out that I never typed in. There are five ways to do it and they are not interchangeable. For each one: what it does, an example from my own data, who in my review uses it, and whether it fits me.</t>
         </is>
@@ -11817,553 +11490,553 @@
     </row>
     <row r="3" ht="8" customHeight="1" s="49"/>
     <row r="4" ht="28" customHeight="1" s="49">
-      <c r="A4" s="160" t="inlineStr">
+      <c r="A4" s="156" t="inlineStr">
         <is>
           <t>The technique</t>
         </is>
       </c>
-      <c r="B4" s="160" t="inlineStr">
+      <c r="B4" s="156" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
-      <c r="C4" s="160" t="inlineStr">
+      <c r="C4" s="156" t="inlineStr">
         <is>
           <t>Example from my data</t>
         </is>
       </c>
-      <c r="D4" s="160" t="inlineStr">
+      <c r="D4" s="156" t="inlineStr">
         <is>
           <t>Who in my review uses it</t>
         </is>
       </c>
-      <c r="E4" s="160" t="inlineStr">
+      <c r="E4" s="156" t="inlineStr">
         <is>
           <t>Fits me</t>
         </is>
       </c>
-      <c r="F4" s="160" t="inlineStr">
+      <c r="F4" s="156" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="49">
-      <c r="A5" s="154" t="inlineStr">
+      <c r="A5" s="157" t="inlineStr">
         <is>
           <t>1. The five ways to reason</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" s="49">
-      <c r="A6" s="155" t="inlineStr">
+      <c r="A6" s="158" t="inlineStr">
         <is>
           <t>RDFS entailment</t>
         </is>
       </c>
-      <c r="B6" s="156" t="inlineStr">
+      <c r="B6" s="159" t="inlineStr">
         <is>
           <t>The cheapest one. If Cleanser is a subclass of Product, then every cleanser is a product.</t>
         </is>
       </c>
-      <c r="C6" s="156" t="inlineStr">
+      <c r="C6" s="159" t="inlineStr">
         <is>
           <t>I say CeraVe Cleanser is a skc:Cleanser. The machine works out it is also a Product. I never typed that.</t>
         </is>
       </c>
-      <c r="D6" s="156" t="inlineStr">
+      <c r="D6" s="159" t="inlineStr">
         <is>
           <t>Abesova gets this free in GraphDB</t>
         </is>
       </c>
-      <c r="E6" s="157" t="inlineStr">
+      <c r="E6" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F6" s="156" t="inlineStr">
+      <c r="F6" s="159" t="inlineStr">
         <is>
           <t>Free and always on. But it only does the hierarchy. Nothing clever.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="49">
-      <c r="A7" s="155" t="inlineStr">
+      <c r="A7" s="158" t="inlineStr">
         <is>
           <t>OWL defined classes</t>
         </is>
       </c>
-      <c r="B7" s="156" t="inlineStr">
+      <c r="B7" s="159" t="inlineStr">
         <is>
           <t>I write the definition of a class, and the reasoner decides who belongs. I never tag anything by hand.</t>
         </is>
       </c>
-      <c r="C7" s="156" t="inlineStr">
+      <c r="C7" s="159" t="inlineStr">
         <is>
           <t>SensitiveSafeProduct = a Product with no restricted ingredient and no fragrance allergen. The reasoner finds all the members itself.</t>
         </is>
       </c>
-      <c r="D7" s="156" t="inlineStr">
+      <c r="D7" s="159" t="inlineStr">
         <is>
           <t>Abesova, OntoCosmetic, COPPER</t>
         </is>
       </c>
-      <c r="E7" s="157" t="inlineStr">
+      <c r="E7" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" s="156" t="inlineStr">
+      <c r="F7" s="159" t="inlineStr">
         <is>
           <t>This is my main mechanism. If I add a product tomorrow it lands in the right classes with no extra work. A database cannot do this.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="49">
-      <c r="A8" s="155" t="inlineStr">
+      <c r="A8" s="158" t="inlineStr">
         <is>
           <t>SWRL rules</t>
         </is>
       </c>
-      <c r="B8" s="156" t="inlineStr">
+      <c r="B8" s="159" t="inlineStr">
         <is>
           <t>If-then rules bolted onto OWL, for things OWL alone cannot say.</t>
         </is>
       </c>
-      <c r="C8" s="156" t="inlineStr">
+      <c r="C8" s="159" t="inlineStr">
         <is>
           <t>If a product has retinol and an AHA, flag a conflict. OWL alone struggles with rules that need two variables.</t>
         </is>
       </c>
-      <c r="D8" s="156" t="inlineStr">
+      <c r="D8" s="159" t="inlineStr">
         <is>
           <t>OntoCosmetic, for its thresholds</t>
         </is>
       </c>
-      <c r="E8" s="157" t="inlineStr">
+      <c r="E8" s="160" t="inlineStr">
         <is>
           <t>maybe</t>
         </is>
       </c>
-      <c r="F8" s="156" t="inlineStr">
+      <c r="F8" s="159" t="inlineStr">
         <is>
           <t>Powerful, but it slows the reasoner and only Pellet or Openllet runs it properly. Two rules at most.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1" s="49">
-      <c r="A9" s="155" t="inlineStr">
+      <c r="A9" s="158" t="inlineStr">
         <is>
           <t>SPARQL CONSTRUCT</t>
         </is>
       </c>
-      <c r="B9" s="156" t="inlineStr">
+      <c r="B9" s="159" t="inlineStr">
         <is>
           <t>A query that writes new triples instead of returning a table.</t>
         </is>
       </c>
-      <c r="C9" s="156" t="inlineStr">
+      <c r="C9" s="159" t="inlineStr">
         <is>
           <t>Construct a triple saying a product suits winter, by combining occlusive with no drying alcohol.</t>
         </is>
       </c>
-      <c r="D9" s="156" t="inlineStr">
+      <c r="D9" s="159" t="inlineStr">
         <is>
           <t>Abesova, to build the OilyScore triples</t>
         </is>
       </c>
-      <c r="E9" s="157" t="inlineStr">
+      <c r="E9" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F9" s="156" t="inlineStr">
+      <c r="F9" s="159" t="inlineStr">
         <is>
           <t>Simple and fast, and I already know SPARQL. But the rules sit in loose .rq files and nothing checks them.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1" s="49">
-      <c r="A10" s="155" t="inlineStr">
+      <c r="A10" s="158" t="inlineStr">
         <is>
           <t>SHACL rules (SHACL-AF)</t>
         </is>
       </c>
-      <c r="B10" s="156" t="inlineStr">
+      <c r="B10" s="159" t="inlineStr">
         <is>
           <t>Rules written in the graph, in Turtle, that add new triples. Also the only standard way to validate.</t>
         </is>
       </c>
-      <c r="C10" s="156" t="inlineStr">
+      <c r="C10" s="159" t="inlineStr">
         <is>
           <t>See section 3 below. This is the one nobody in my review uses.</t>
         </is>
       </c>
-      <c r="D10" s="156" t="inlineStr">
+      <c r="D10" s="159" t="inlineStr">
         <is>
           <t>Nobody. 0 of 28 papers.</t>
         </is>
       </c>
-      <c r="E10" s="157" t="inlineStr">
+      <c r="E10" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F10" s="156" t="inlineStr">
+      <c r="F10" s="159" t="inlineStr">
         <is>
           <t>Two jobs in one language: catch bad data, and infer new facts. And it is a gap I can claim.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" s="49">
-      <c r="A11" s="154" t="inlineStr">
+      <c r="A11" s="157" t="inlineStr">
         <is>
           <t>2. Why OWL and SHACL are not the same thing</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1" s="49">
-      <c r="A12" s="155" t="inlineStr">
+      <c r="A12" s="158" t="inlineStr">
         <is>
           <t>OWL is open world</t>
         </is>
       </c>
-      <c r="B12" s="156" t="inlineStr">
+      <c r="B12" s="159" t="inlineStr">
         <is>
           <t>If something is not written down, OWL assumes it might still be true. It never complains about missing data.</t>
         </is>
       </c>
-      <c r="C12" s="156" t="inlineStr">
+      <c r="C12" s="159" t="inlineStr">
         <is>
           <t>I say a product must have one price. A product has two. OWL does not error. It decides the two prices are the same thing.</t>
         </is>
       </c>
-      <c r="D12" s="156" t="inlineStr">
+      <c r="D12" s="159" t="inlineStr">
         <is>
           <t>Everyone using OWL</t>
         </is>
       </c>
-      <c r="E12" s="157" t="inlineStr">
+      <c r="E12" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F12" s="156" t="inlineStr">
+      <c r="F12" s="159" t="inlineStr">
         <is>
           <t>Right for inferring. Wrong for checking my data is clean.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1" s="49">
-      <c r="A13" s="155" t="inlineStr">
+      <c r="A13" s="158" t="inlineStr">
         <is>
           <t>SHACL is closed world</t>
         </is>
       </c>
-      <c r="B13" s="156" t="inlineStr">
+      <c r="B13" s="159" t="inlineStr">
         <is>
           <t>What is not in the graph is treated as false. It reports an error and points at the exact triple.</t>
         </is>
       </c>
-      <c r="C13" s="156" t="inlineStr">
+      <c r="C13" s="159" t="inlineStr">
         <is>
           <t>Same case. SHACL says 'product X has 2 values for hasPrice, maximum is 1', and names X.</t>
         </is>
       </c>
-      <c r="D13" s="156" t="inlineStr">
+      <c r="D13" s="159" t="inlineStr">
         <is>
           <t>Nobody in my review</t>
         </is>
       </c>
-      <c r="E13" s="157" t="inlineStr">
+      <c r="E13" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F13" s="156" t="inlineStr">
+      <c r="F13" s="159" t="inlineStr">
         <is>
           <t>This is what I want when validating 12,629 rows. OWL cannot do it.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1" s="49">
-      <c r="A14" s="155" t="inlineStr">
+      <c r="A14" s="158" t="inlineStr">
         <is>
           <t>The mistake to avoid</t>
         </is>
       </c>
-      <c r="B14" s="156" t="inlineStr">
+      <c r="B14" s="159" t="inlineStr">
         <is>
           <t>People write owl:maxCardinality thinking it is a constraint. It is not. It is an instruction to infer.</t>
         </is>
       </c>
-      <c r="C14" s="156" t="inlineStr">
+      <c r="C14" s="159" t="inlineStr">
         <is>
           <t>The most common beginner mistake in OWL. Worth one sentence in my chapter.</t>
         </is>
       </c>
-      <c r="D14" s="156" t="inlineStr"/>
-      <c r="E14" s="157" t="inlineStr"/>
-      <c r="F14" s="156" t="inlineStr">
+      <c r="D14" s="159" t="inlineStr"/>
+      <c r="E14" s="160" t="inlineStr"/>
+      <c r="F14" s="159" t="inlineStr">
         <is>
           <t>Source: Knublauch, 'SHACL and OWL Compared', spinrdf.org/shacl-and-owl.html</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="49">
-      <c r="A15" s="154" t="inlineStr">
+      <c r="A15" s="157" t="inlineStr">
         <is>
           <t>3. What SHACL would do in my thesis</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1" s="49">
-      <c r="A16" s="155" t="inlineStr">
+      <c r="A16" s="158" t="inlineStr">
         <is>
           <t>Job 1. Guard the dataset</t>
         </is>
       </c>
-      <c r="B16" s="156" t="inlineStr">
+      <c r="B16" s="159" t="inlineStr">
         <is>
           <t>Check every product before it enters the graph.</t>
         </is>
       </c>
-      <c r="C16" s="156" t="inlineStr">
+      <c r="C16" s="159" t="inlineStr">
         <is>
           <t>Every product must have at least one ingredient, one price, a country from a fixed list, and a rating between 0 and 5. Run once, get a report naming every bad row.</t>
         </is>
       </c>
-      <c r="D16" s="156" t="inlineStr"/>
-      <c r="E16" s="157" t="inlineStr">
+      <c r="D16" s="159" t="inlineStr"/>
+      <c r="E16" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F16" s="156" t="inlineStr">
+      <c r="F16" s="159" t="inlineStr">
         <is>
           <t>I have 12,629 rows from eight sources. Something is wrong in there. The report goes in the appendix as evidence.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="49">
-      <c r="A17" s="155" t="inlineStr">
+      <c r="A17" s="158" t="inlineStr">
         <is>
           <t>Job 2. Enforce my evidence rule</t>
         </is>
       </c>
-      <c r="B17" s="156" t="inlineStr">
+      <c r="B17" s="159" t="inlineStr">
         <is>
           <t>The rule I keep saying matters. No claim without a source.</t>
         </is>
       </c>
-      <c r="C17" s="156" t="inlineStr">
+      <c r="C17" s="159" t="inlineStr">
         <is>
           <t>Every ingredient with a CosIng annex status must carry prov:wasAttributedTo and a date. SHACL refuses it otherwise.</t>
         </is>
       </c>
-      <c r="D17" s="156" t="inlineStr"/>
-      <c r="E17" s="157" t="inlineStr">
+      <c r="D17" s="159" t="inlineStr"/>
+      <c r="E17" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F17" s="156" t="inlineStr">
+      <c r="F17" s="159" t="inlineStr">
         <is>
           <t>This turns my provenance design from a promise into something a machine enforces. The strongest single use for me.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" s="49">
-      <c r="A18" s="155" t="inlineStr">
+      <c r="A18" s="158" t="inlineStr">
         <is>
           <t>Job 3. Infer, with sh:TripleRule</t>
         </is>
       </c>
-      <c r="B18" s="156" t="inlineStr">
+      <c r="B18" s="159" t="inlineStr">
         <is>
           <t>Add a triple when a condition holds. The same job as a defined class, but easier to read.</t>
         </is>
       </c>
-      <c r="C18" s="156" t="inlineStr">
+      <c r="C18" s="159" t="inlineStr">
         <is>
           <t>If a product has three or more barrier lipids, add rdf:type BarrierRepairProduct.</t>
         </is>
       </c>
-      <c r="D18" s="156" t="inlineStr"/>
-      <c r="E18" s="157" t="inlineStr">
+      <c r="D18" s="159" t="inlineStr"/>
+      <c r="E18" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F18" s="156" t="inlineStr">
+      <c r="F18" s="159" t="inlineStr">
         <is>
           <t>Compare with OWL. OWL can only ever infer types and sameAs. SHACL can infer any triple.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" s="49">
-      <c r="A19" s="155" t="inlineStr">
+      <c r="A19" s="158" t="inlineStr">
         <is>
           <t>Job 4. Count, with sh:SPARQLRule</t>
         </is>
       </c>
-      <c r="B19" s="156" t="inlineStr">
+      <c r="B19" s="159" t="inlineStr">
         <is>
           <t>A rule that does arithmetic and writes the answer back.</t>
         </is>
       </c>
-      <c r="C19" s="156" t="inlineStr">
+      <c r="C19" s="159" t="inlineStr">
         <is>
           <t>Count how many EU-restricted ingredients a product has, and store it as a number I can sort on.</t>
         </is>
       </c>
-      <c r="D19" s="156" t="inlineStr"/>
-      <c r="E19" s="157" t="inlineStr">
+      <c r="D19" s="159" t="inlineStr"/>
+      <c r="E19" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F19" s="156" t="inlineStr">
+      <c r="F19" s="159" t="inlineStr">
         <is>
           <t>OWL cannot count. This is the honest limit of OWL and the cleanest reason to add SHACL.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="49">
-      <c r="A20" s="154" t="inlineStr">
+      <c r="A20" s="157" t="inlineStr">
         <is>
           <t>4. How to run it</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" s="49">
-      <c r="A21" s="155" t="inlineStr">
+      <c r="A21" s="158" t="inlineStr">
         <is>
           <t>pySHACL</t>
         </is>
       </c>
-      <c r="B21" s="156" t="inlineStr">
+      <c r="B21" s="159" t="inlineStr">
         <is>
           <t>Python. pip install pyshacl, then one line.</t>
         </is>
       </c>
-      <c r="C21" s="156" t="inlineStr">
+      <c r="C21" s="159" t="inlineStr">
         <is>
           <t>pyshacl -s shapes.ttl -f human data.ttl</t>
         </is>
       </c>
-      <c r="D21" s="156" t="inlineStr"/>
-      <c r="E21" s="157" t="inlineStr">
+      <c r="D21" s="159" t="inlineStr"/>
+      <c r="E21" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F21" s="156" t="inlineStr">
+      <c r="F21" s="159" t="inlineStr">
         <is>
           <t>My pipeline is Python and it pairs with RDFLib. The slowest of the three, but my graph is 1.8 million triples, which is small.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" s="49">
-      <c r="A22" s="155" t="inlineStr">
+      <c r="A22" s="158" t="inlineStr">
         <is>
           <t>Apache Jena SHACL</t>
         </is>
       </c>
-      <c r="B22" s="156" t="inlineStr">
+      <c r="B22" s="159" t="inlineStr">
         <is>
           <t>Java. The fastest of the three in published benchmarks.</t>
         </is>
       </c>
-      <c r="C22" s="156" t="inlineStr">
+      <c r="C22" s="159" t="inlineStr">
         <is>
           <t>Command line or library. It also reads SHACL-C, a compact syntax that is easier to read than Turtle.</t>
         </is>
       </c>
-      <c r="D22" s="156" t="inlineStr"/>
-      <c r="E22" s="157" t="inlineStr">
+      <c r="D22" s="159" t="inlineStr"/>
+      <c r="E22" s="160" t="inlineStr">
         <is>
           <t>maybe</t>
         </is>
       </c>
-      <c r="F22" s="156" t="inlineStr">
+      <c r="F22" s="159" t="inlineStr">
         <is>
           <t>Benchmarked around four times faster than pySHACL. Only worth it if pySHACL gets slow.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" s="49">
-      <c r="A23" s="155" t="inlineStr">
+      <c r="A23" s="158" t="inlineStr">
         <is>
           <t>TopBraid SHACL API</t>
         </is>
       </c>
-      <c r="B23" s="156" t="inlineStr">
+      <c r="B23" s="159" t="inlineStr">
         <is>
           <t>Java, from the people who wrote the spec. The reference implementation.</t>
         </is>
       </c>
-      <c r="C23" s="156" t="inlineStr">
+      <c r="C23" s="159" t="inlineStr">
         <is>
           <t>It defines correct behaviour when the other engines disagree.</t>
         </is>
       </c>
-      <c r="D23" s="156" t="inlineStr"/>
-      <c r="E23" s="157" t="inlineStr">
+      <c r="D23" s="159" t="inlineStr"/>
+      <c r="E23" s="160" t="inlineStr">
         <is>
           <t>maybe</t>
         </is>
       </c>
-      <c r="F23" s="156" t="inlineStr">
+      <c r="F23" s="159" t="inlineStr">
         <is>
           <t>Useful to check against if a result looks wrong.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" s="49">
-      <c r="A24" s="155" t="inlineStr">
+      <c r="A24" s="158" t="inlineStr">
         <is>
           <t>GraphDB</t>
         </is>
       </c>
-      <c r="B24" s="156" t="inlineStr">
+      <c r="B24" s="159" t="inlineStr">
         <is>
           <t>My triple store has SHACL validation built in.</t>
         </is>
       </c>
-      <c r="C24" s="156" t="inlineStr">
+      <c r="C24" s="159" t="inlineStr">
         <is>
           <t>Turn it on when creating the repository, and bad data is rejected at load time.</t>
         </is>
       </c>
-      <c r="D24" s="156" t="inlineStr"/>
-      <c r="E24" s="157" t="inlineStr">
+      <c r="D24" s="159" t="inlineStr"/>
+      <c r="E24" s="160" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F24" s="156" t="inlineStr">
+      <c r="F24" s="159" t="inlineStr">
         <is>
           <t>No extra tooling. This is where I would start.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" s="49">
-      <c r="A26" s="154" t="inlineStr">
+      <c r="A26" s="157" t="inlineStr">
         <is>
           <t>The code. Put these four in a file called shapes.ttl</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="49">
-      <c r="A28" s="164" t="inlineStr">
+      <c r="A28" s="165" t="inlineStr">
         <is>
           <t>Job 1. Catch bad data. Plain SHACL Core, no extras.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" s="49">
-      <c r="A29" s="165" t="inlineStr">
+      <c r="A29" s="166" t="inlineStr">
         <is>
           <t>sk:ProductShape
     a sh:NodeShape ;
@@ -12405,14 +12078,14 @@
     <row r="47" ht="13" customHeight="1" s="49"/>
     <row r="48" ht="13" customHeight="1" s="49"/>
     <row r="50" ht="18" customHeight="1" s="49">
-      <c r="A50" s="164" t="inlineStr">
+      <c r="A50" s="165" t="inlineStr">
         <is>
           <t>Job 2. No claim without a source. My provenance rule, enforced.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" s="49">
-      <c r="A51" s="165" t="inlineStr">
+      <c r="A51" s="166" t="inlineStr">
         <is>
           <t>sk:AnnexClaimShape
     a sh:NodeShape ;
@@ -12445,14 +12118,14 @@
     <row r="64" ht="13" customHeight="1" s="49"/>
     <row r="65" ht="13" customHeight="1" s="49"/>
     <row r="67" ht="18" customHeight="1" s="49">
-      <c r="A67" s="164" t="inlineStr">
+      <c r="A67" s="165" t="inlineStr">
         <is>
           <t>Job 3. Infer a new type. sh:TripleRule, from SHACL Advanced Features.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1" s="49">
-      <c r="A68" s="165" t="inlineStr">
+      <c r="A68" s="166" t="inlineStr">
         <is>
           <t>sk:BarrierRepairRule
     a sh:NodeShape ;
@@ -12479,14 +12152,14 @@
     <row r="77" ht="13" customHeight="1" s="49"/>
     <row r="78" ht="13" customHeight="1" s="49"/>
     <row r="80" ht="18" customHeight="1" s="49">
-      <c r="A80" s="164" t="inlineStr">
+      <c r="A80" s="165" t="inlineStr">
         <is>
           <t>Job 4. Count something. OWL cannot do this. sh:SPARQLRule.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="13" customHeight="1" s="49">
-      <c r="A81" s="165" t="inlineStr">
+      <c r="A81" s="166" t="inlineStr">
         <is>
           <t>sk:RestrictedCountRule
     a sh:NodeShape ;
@@ -12519,14 +12192,14 @@
     <row r="93" ht="13" customHeight="1" s="49"/>
     <row r="94" ht="13" customHeight="1" s="49"/>
     <row r="96" ht="24" customHeight="1" s="49">
-      <c r="A96" s="154" t="inlineStr">
+      <c r="A96" s="157" t="inlineStr">
         <is>
           <t>The sentence for my chapter</t>
         </is>
       </c>
     </row>
     <row r="97" ht="62" customHeight="1" s="49">
-      <c r="A97" s="163" t="inlineStr">
+      <c r="A97" s="164" t="inlineStr">
         <is>
           <t>"None of the 28 reviewed systems reports any use of SHACL. Validation of the underlying data, and the enforcement of provenance constraints, are therefore unaddressed in the existing skincare ontology literature."
 That is a small, true, defensible gap claim, and it costs one afternoon of work to earn it.</t>
@@ -12574,14 +12247,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="49">
-      <c r="A1" s="158" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>Abesova 2023, the paper my supervisor sent</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" s="49">
-      <c r="A2" s="159" t="inlineStr">
+      <c r="A2" s="155" t="inlineStr">
         <is>
           <t>A student course project, so it is not peer reviewed and I have to say so. But the main idea in it is the one my thesis uses, and its third limitation is my contribution.</t>
         </is>
@@ -12589,472 +12262,472 @@
     </row>
     <row r="3" ht="8" customHeight="1" s="49"/>
     <row r="4" ht="24" customHeight="1" s="49">
-      <c r="A4" s="154" t="inlineStr">
+      <c r="A4" s="157" t="inlineStr">
         <is>
           <t>1. What it is</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" s="49">
-      <c r="B5" s="162" t="inlineStr">
+      <c r="B5" s="163" t="inlineStr">
         <is>
           <t>Full title</t>
         </is>
       </c>
-      <c r="C5" s="161" t="inlineStr">
+      <c r="C5" s="162" t="inlineStr">
         <is>
           <t>Skincare Ontology, Final Project</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1" s="49">
-      <c r="B6" s="162" t="inlineStr">
+      <c r="B6" s="163" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="C6" s="161" t="inlineStr">
+      <c r="C6" s="162" t="inlineStr">
         <is>
           <t>Sara Abesova, Karolina Hajkova, Yozlem Ramadan, Malgorzata Zdych</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" s="49">
-      <c r="B7" s="162" t="inlineStr">
+      <c r="B7" s="163" t="inlineStr">
         <is>
           <t>Where</t>
         </is>
       </c>
-      <c r="C7" s="161" t="inlineStr">
+      <c r="C7" s="162" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam, course 'Knowledge and Data', Group 31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" s="49">
-      <c r="B8" s="162" t="inlineStr">
+      <c r="B8" s="163" t="inlineStr">
         <is>
           <t>What kind of thing</t>
         </is>
       </c>
-      <c r="C8" s="161" t="inlineStr">
+      <c r="C8" s="162" t="inlineStr">
         <is>
           <t>A student course project. Not peer reviewed, not in a journal. I have to say this or a supervisor will catch it.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" s="49">
-      <c r="B9" s="162" t="inlineStr">
+      <c r="B9" s="163" t="inlineStr">
         <is>
           <t>Why I still care</t>
         </is>
       </c>
-      <c r="C9" s="161" t="inlineStr">
+      <c r="C9" s="162" t="inlineStr">
         <is>
           <t>The main idea in it is the mechanism my thesis is built on, and their third limitation is my contribution written in their own words.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" s="49">
-      <c r="B10" s="162" t="inlineStr">
+      <c r="B10" s="163" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C10" s="161" t="inlineStr">
+      <c r="C10" s="162" t="inlineStr">
         <is>
           <t>36 classes, 6 object properties, 6 data properties</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" s="49">
-      <c r="B11" s="162" t="inlineStr">
+      <c r="B11" s="163" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C11" s="161" t="inlineStr">
+      <c r="C11" s="162" t="inlineStr">
         <is>
           <t>Middle-out. Start from a base ontology and let the data pull it wider.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" s="49">
-      <c r="B12" s="162" t="inlineStr">
+      <c r="B12" s="163" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C12" s="161" t="inlineStr">
+      <c r="C12" s="162" t="inlineStr">
         <is>
           <t>OntoRefine, GraphDB, SPARQL, DBpedia, Jupyter, pandas, folium. No Protege.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" s="49">
-      <c r="B13" s="162" t="inlineStr">
+      <c r="B13" s="163" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C13" s="161" t="inlineStr">
+      <c r="C13" s="162" t="inlineStr">
         <is>
           <t>1. A Sephora review CSV found on GitHub (agorina91/final_project). 2. A hand-made CSV of countries with Sephora links. 3. DBpedia, live, for capital city coordinates.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" s="49">
-      <c r="B14" s="162" t="inlineStr">
+      <c r="B14" s="163" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C14" s="161" t="inlineStr">
+      <c r="C14" s="162" t="inlineStr">
         <is>
           <t>9 products (3 cleansers, 3 moisturisers, 3 treatments), plus the local Sephora link, plus whether there is a physical shop</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="49">
-      <c r="A16" s="154" t="inlineStr">
+      <c r="A16" s="157" t="inlineStr">
         <is>
           <t>2. What they did, step by step</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" s="49">
-      <c r="A17" s="160" t="inlineStr"/>
-      <c r="B17" s="160" t="inlineStr">
+      <c r="A17" s="156" t="inlineStr"/>
+      <c r="B17" s="156" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C17" s="160" t="inlineStr">
+      <c r="C17" s="156" t="inlineStr">
         <is>
           <t>What they did</t>
         </is>
       </c>
-      <c r="D17" s="160" t="inlineStr">
+      <c r="D17" s="156" t="inlineStr">
         <is>
           <t>Tool</t>
         </is>
       </c>
-      <c r="E17" s="160" t="inlineStr">
+      <c r="E17" s="156" t="inlineStr">
         <is>
           <t>My note</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" s="49">
-      <c r="A18" s="161" t="inlineStr">
+      <c r="A18" s="162" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B18" s="162" t="inlineStr">
+      <c r="B18" s="163" t="inlineStr">
         <is>
           <t>Start from a base ontology</t>
         </is>
       </c>
-      <c r="C18" s="161" t="inlineStr">
+      <c r="C18" s="162" t="inlineStr">
         <is>
           <t>One teammate had already built a small skincare ontology earlier in the course.</t>
         </is>
       </c>
-      <c r="D18" s="161" t="inlineStr">
+      <c r="D18" s="162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E18" s="161" t="inlineStr">
+      <c r="E18" s="162" t="inlineStr">
         <is>
           <t>This is why it is middle-out and not top-down. They did not start from nothing.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" s="49">
-      <c r="A19" s="161" t="inlineStr">
+      <c r="A19" s="162" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B19" s="162" t="inlineStr">
+      <c r="B19" s="163" t="inlineStr">
         <is>
           <t>Find outside data</t>
         </is>
       </c>
-      <c r="C19" s="161" t="inlineStr">
+      <c r="C19" s="162" t="inlineStr">
         <is>
           <t>They searched the web and found a CSV of Sephora product reviews on GitHub.</t>
         </is>
       </c>
-      <c r="D19" s="161" t="inlineStr">
+      <c r="D19" s="162" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E19" s="161" t="inlineStr">
+      <c r="E19" s="162" t="inlineStr">
         <is>
           <t>They say this was the hardest part of the project. Finding data usually is.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1" s="49">
-      <c r="A20" s="161" t="inlineStr">
+      <c r="A20" s="162" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B20" s="162" t="inlineStr">
+      <c r="B20" s="163" t="inlineStr">
         <is>
           <t>Clean it</t>
         </is>
       </c>
-      <c r="C20" s="161" t="inlineStr">
+      <c r="C20" s="162" t="inlineStr">
         <is>
           <t>Deleted columns that did not matter, such as Eye Color and Hair Color. Checked nothing important was removed by accident.</t>
         </is>
       </c>
-      <c r="D20" s="161" t="inlineStr">
+      <c r="D20" s="162" t="inlineStr">
         <is>
           <t>by hand</t>
         </is>
       </c>
-      <c r="E20" s="161" t="inlineStr">
+      <c r="E20" s="162" t="inlineStr">
         <is>
           <t>The same thing I did. Boring and necessary.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" s="49">
-      <c r="A21" s="161" t="inlineStr">
+      <c r="A21" s="162" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B21" s="162" t="inlineStr">
+      <c r="B21" s="163" t="inlineStr">
         <is>
           <t>Turn the CSV into RDF</t>
         </is>
       </c>
-      <c r="C21" s="161" t="inlineStr">
+      <c r="C21" s="162" t="inlineStr">
         <is>
           <t>Loaded the CSV into OntoRefine and drew the mapping: which column becomes a subject, which becomes a predicate.</t>
         </is>
       </c>
-      <c r="D21" s="161" t="inlineStr">
+      <c r="D21" s="162" t="inlineStr">
         <is>
           <t>OntoRefine, inside GraphDB</t>
         </is>
       </c>
-      <c r="E21" s="161" t="inlineStr">
+      <c r="E21" s="162" t="inlineStr">
         <is>
           <t>This is the step Morph-KGC does for me. Theirs is point-and-click, mine is a file I can put in the appendix.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1" s="49">
-      <c r="A22" s="161" t="inlineStr">
+      <c r="A22" s="162" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B22" s="162" t="inlineStr">
+      <c r="B22" s="163" t="inlineStr">
         <is>
           <t>Build the graphs and export</t>
         </is>
       </c>
-      <c r="C22" s="161" t="inlineStr">
+      <c r="C22" s="162" t="inlineStr">
         <is>
           <t>SPARQL CONSTRUCT, one graph at a time, downloaded as nine separate Turtle files, then all imported into one default graph.</t>
         </is>
       </c>
-      <c r="D22" s="161" t="inlineStr">
+      <c r="D22" s="162" t="inlineStr">
         <is>
           <t>SPARQL CONSTRUCT</t>
         </is>
       </c>
-      <c r="E22" s="161" t="inlineStr">
+      <c r="E22" s="162" t="inlineStr">
         <is>
           <t>Nine files by hand is fragile. To rerun it they have to redo all nine.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1" s="49">
-      <c r="A23" s="161" t="inlineStr">
+      <c r="A23" s="162" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B23" s="162" t="inlineStr">
+      <c r="B23" s="163" t="inlineStr">
         <is>
           <t>Glue the two vocabularies together</t>
         </is>
       </c>
-      <c r="C23" s="161" t="inlineStr">
+      <c r="C23" s="162" t="inlineStr">
         <is>
           <t>The CSV had its own class names and the base ontology had different ones, so they declared rdf:Cleanser owl:equivalentClass skc:Cleanser.</t>
         </is>
       </c>
-      <c r="D23" s="161" t="inlineStr">
+      <c r="D23" s="162" t="inlineStr">
         <is>
           <t>GraphDB class restrictions</t>
         </is>
       </c>
-      <c r="E23" s="161" t="inlineStr">
+      <c r="E23" s="162" t="inlineStr">
         <is>
           <t>This is real ontology work, and it is the honest answer to 'how do you merge two sources'.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1" s="49">
-      <c r="A24" s="161" t="inlineStr">
+      <c r="A24" s="162" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="162" t="inlineStr">
+      <c r="B24" s="163" t="inlineStr">
         <is>
           <t>Add the main idea</t>
         </is>
       </c>
-      <c r="C24" s="161" t="inlineStr">
+      <c r="C24" s="162" t="inlineStr">
         <is>
           <t>Compute an average rating per skin type, store it as hasOilyScore, then define the class OilySkinProducts as 'hasOilyScore value 5'. The reasoner fills the class.</t>
         </is>
       </c>
-      <c r="D24" s="161" t="inlineStr">
+      <c r="D24" s="162" t="inlineStr">
         <is>
           <t>OWL hasValue, GraphDB reasoner</t>
         </is>
       </c>
-      <c r="E24" s="161" t="inlineStr">
+      <c r="E24" s="162" t="inlineStr">
         <is>
           <t>This is the part I use. See section 4.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" s="49">
-      <c r="A25" s="161" t="inlineStr">
+      <c r="A25" s="162" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B25" s="162" t="inlineStr">
+      <c r="B25" s="163" t="inlineStr">
         <is>
           <t>Reach out to DBpedia</t>
         </is>
       </c>
-      <c r="C25" s="161" t="inlineStr">
+      <c r="C25" s="162" t="inlineStr">
         <is>
           <t>SPARQL against the live DBpedia endpoint. Country to capital city to geo:lat and geo:long, then draw a map.</t>
         </is>
       </c>
-      <c r="D25" s="161" t="inlineStr">
+      <c r="D25" s="162" t="inlineStr">
         <is>
           <t>DBpedia, geo: and dbo:</t>
         </is>
       </c>
-      <c r="E25" s="161" t="inlineStr">
+      <c r="E25" s="162" t="inlineStr">
         <is>
           <t>They typed no coordinates at all. This is what reuse looks like in practice.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1" s="49">
-      <c r="A26" s="161" t="inlineStr">
+      <c r="A26" s="162" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B26" s="162" t="inlineStr">
+      <c r="B26" s="163" t="inlineStr">
         <is>
           <t>Recommend</t>
         </is>
       </c>
-      <c r="C26" s="161" t="inlineStr">
+      <c r="C26" s="162" t="inlineStr">
         <is>
           <t>Query reviews from people with the same skin type and skin tone, rank by rating, take the top 3 per category. If there is not enough data, fall back to the defined class.</t>
         </is>
       </c>
-      <c r="D26" s="161" t="inlineStr">
+      <c r="D26" s="162" t="inlineStr">
         <is>
           <t>SPARQL, Jupyter</t>
         </is>
       </c>
-      <c r="E26" s="161" t="inlineStr">
+      <c r="E26" s="162" t="inlineStr">
         <is>
           <t>The fallback is smart. Their thin-data problem is my cold-start problem.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1" s="49">
-      <c r="A27" s="161" t="inlineStr">
+      <c r="A27" s="162" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="162" t="inlineStr">
+      <c r="B27" s="163" t="inlineStr">
         <is>
           <t>Show it</t>
         </is>
       </c>
-      <c r="C27" s="161" t="inlineStr">
+      <c r="C27" s="162" t="inlineStr">
         <is>
           <t>Two pie charts, counts per skin type and per skin tone, and a world map of Sephora countries.</t>
         </is>
       </c>
-      <c r="D27" s="161" t="inlineStr">
+      <c r="D27" s="162" t="inlineStr">
         <is>
           <t>pandas, folium</t>
         </is>
       </c>
-      <c r="E27" s="161" t="inlineStr">
+      <c r="E27" s="162" t="inlineStr">
         <is>
           <t>The pie charts exist so the user can judge how much data the answer rests on. I like that.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="49">
-      <c r="A29" s="154" t="inlineStr">
+      <c r="A29" s="157" t="inlineStr">
         <is>
           <t>3. The pipeline, in words</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="49">
-      <c r="B30" s="166" t="inlineStr">
+      <c r="B30" s="167" t="inlineStr">
         <is>
           <t>Sephora review CSV  -&gt;  OntoRefine  -&gt;  9 Turtle files  -&gt;  GraphDB  -&gt;  reasoner  -&gt;  SPARQL  -&gt;  9 products</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="49">
-      <c r="B31" s="166" t="inlineStr"/>
+      <c r="B31" s="167" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="49">
-      <c r="B32" s="166" t="inlineStr">
+      <c r="B32" s="167" t="inlineStr">
         <is>
           <t>side input 1   a CSV they typed themselves: country -&gt; Sephora link</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="49">
-      <c r="B33" s="166" t="inlineStr">
+      <c r="B33" s="167" t="inlineStr">
         <is>
           <t>side input 2   DBpedia, live: country -&gt; capital city -&gt; geo:lat and geo:long, for the map</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" s="49">
-      <c r="A35" s="154" t="inlineStr">
+      <c r="A35" s="157" t="inlineStr">
         <is>
           <t>4. The main idea, and it is the one I use</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" s="49">
-      <c r="B36" s="167" t="inlineStr">
+      <c r="B36" s="168" t="inlineStr">
         <is>
           <t>They never tag a product as good for oily skin. Not once. Instead:
    Step 1   Query all reviews written by people with oily skin, average the stars,
@@ -13098,437 +12771,437 @@
     <row r="57" ht="14" customHeight="1" s="49"/>
     <row r="58" ht="14" customHeight="1" s="49"/>
     <row r="60" ht="24" customHeight="1" s="49">
-      <c r="A60" s="154" t="inlineStr">
+      <c r="A60" s="157" t="inlineStr">
         <is>
           <t>5. Their classes and properties</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1" s="49">
-      <c r="A61" s="160" t="inlineStr"/>
-      <c r="B61" s="160" t="inlineStr">
+      <c r="A61" s="156" t="inlineStr"/>
+      <c r="B61" s="156" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="C61" s="160" t="inlineStr">
+      <c r="C61" s="156" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D61" s="160" t="inlineStr"/>
-      <c r="E61" s="160" t="inlineStr">
+      <c r="D61" s="156" t="inlineStr"/>
+      <c r="E61" s="156" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="49">
-      <c r="B62" s="168" t="inlineStr">
+      <c r="B62" s="169" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C62" s="169" t="inlineStr">
+      <c r="C62" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D62" s="161" t="inlineStr">
+      <c r="D62" s="162" t="inlineStr">
         <is>
           <t>Where the user lives</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="49">
-      <c r="B63" s="168" t="inlineStr">
+      <c r="B63" s="169" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="C63" s="169" t="inlineStr">
+      <c r="C63" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D63" s="161" t="inlineStr"/>
+      <c r="D63" s="162" t="inlineStr"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="49">
-      <c r="B64" s="168" t="inlineStr">
+      <c r="B64" s="169" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C64" s="169" t="inlineStr">
+      <c r="C64" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D64" s="161" t="inlineStr">
+      <c r="D64" s="162" t="inlineStr">
         <is>
           <t>Cleanser, Moisturizer, Treatment</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="49">
-      <c r="B65" s="168" t="inlineStr">
+      <c r="B65" s="169" t="inlineStr">
         <is>
           <t xml:space="preserve">  Treatment</t>
         </is>
       </c>
-      <c r="C65" s="169" t="inlineStr">
+      <c r="C65" s="170" t="inlineStr">
         <is>
           <t>subclass</t>
         </is>
       </c>
-      <c r="D65" s="161" t="inlineStr">
+      <c r="D65" s="162" t="inlineStr">
         <is>
           <t>and under it: Exfoliant (Chemical, Physical), Serum, Toner</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="49">
-      <c r="B66" s="168" t="inlineStr">
+      <c r="B66" s="169" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C66" s="169" t="inlineStr">
+      <c r="C66" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D66" s="161" t="inlineStr"/>
+      <c r="D66" s="162" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="49">
-      <c r="B67" s="170" t="inlineStr">
+      <c r="B67" s="171" t="inlineStr">
         <is>
           <t xml:space="preserve">  Oily Skin Products</t>
         </is>
       </c>
-      <c r="C67" s="171" t="inlineStr">
+      <c r="C67" s="172" t="inlineStr">
         <is>
           <t>defined</t>
         </is>
       </c>
-      <c r="D67" s="161">
+      <c r="D67" s="162">
         <f> hasOilyScore value 5      the reasoner fills this</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="49">
-      <c r="B68" s="170" t="inlineStr">
+      <c r="B68" s="171" t="inlineStr">
         <is>
           <t xml:space="preserve">  Dry Skin Products</t>
         </is>
       </c>
-      <c r="C68" s="171" t="inlineStr">
+      <c r="C68" s="172" t="inlineStr">
         <is>
           <t>defined</t>
         </is>
       </c>
-      <c r="D68" s="161">
+      <c r="D68" s="162">
         <f> hasDryScore value 5</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="49">
-      <c r="B69" s="170" t="inlineStr">
+      <c r="B69" s="171" t="inlineStr">
         <is>
           <t xml:space="preserve">  Normal Skin Products</t>
         </is>
       </c>
-      <c r="C69" s="171" t="inlineStr">
+      <c r="C69" s="172" t="inlineStr">
         <is>
           <t>defined</t>
         </is>
       </c>
-      <c r="D69" s="161">
+      <c r="D69" s="162">
         <f> hasNormalScore value 5</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="49">
-      <c r="B70" s="170" t="inlineStr">
+      <c r="B70" s="171" t="inlineStr">
         <is>
           <t xml:space="preserve">  Combination Skin Products</t>
         </is>
       </c>
-      <c r="C70" s="171" t="inlineStr">
+      <c r="C70" s="172" t="inlineStr">
         <is>
           <t>defined</t>
         </is>
       </c>
-      <c r="D70" s="161">
+      <c r="D70" s="162">
         <f> hasCombinationScore value 5</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="49">
-      <c r="B71" s="168" t="inlineStr">
+      <c r="B71" s="169" t="inlineStr">
         <is>
           <t>Review Id</t>
         </is>
       </c>
-      <c r="C71" s="169" t="inlineStr">
+      <c r="C71" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D71" s="161" t="inlineStr">
+      <c r="D71" s="162" t="inlineStr">
         <is>
           <t>One review by one person</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="49">
-      <c r="B72" s="168" t="inlineStr">
+      <c r="B72" s="169" t="inlineStr">
         <is>
           <t>Rating Stars</t>
         </is>
       </c>
-      <c r="C72" s="169" t="inlineStr">
+      <c r="C72" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D72" s="161" t="inlineStr"/>
+      <c r="D72" s="162" t="inlineStr"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="49">
-      <c r="B73" s="168" t="inlineStr">
+      <c r="B73" s="169" t="inlineStr">
         <is>
           <t>Skin Tone</t>
         </is>
       </c>
-      <c r="C73" s="169" t="inlineStr">
+      <c r="C73" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D73" s="161" t="inlineStr">
+      <c r="D73" s="162" t="inlineStr">
         <is>
           <t>9 values: Porcelain, Fair, Light, Medium, Olive, Tan, Deep, Dark, Ebony</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="49">
-      <c r="B74" s="168" t="inlineStr">
+      <c r="B74" s="169" t="inlineStr">
         <is>
           <t>Skin Type</t>
         </is>
       </c>
-      <c r="C74" s="169" t="inlineStr">
+      <c r="C74" s="170" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D74" s="161" t="inlineStr">
+      <c r="D74" s="162" t="inlineStr">
         <is>
           <t>4 values: Oily, Dry, Normal, Combination</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="49">
-      <c r="B76" s="172" t="inlineStr">
+      <c r="B76" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C76" s="168" t="inlineStr">
+      <c r="C76" s="169" t="inlineStr">
         <is>
           <t>Product hasBrand Brand</t>
         </is>
       </c>
-      <c r="D76" s="173" t="inlineStr"/>
+      <c r="D76" s="174" t="inlineStr"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="49">
-      <c r="B77" s="172" t="inlineStr">
+      <c r="B77" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C77" s="168" t="inlineStr">
+      <c r="C77" s="169" t="inlineStr">
         <is>
           <t>Review Id hasSkinType Skin Type</t>
         </is>
       </c>
-      <c r="D77" s="173" t="inlineStr"/>
+      <c r="D77" s="174" t="inlineStr"/>
     </row>
     <row r="78" ht="15" customHeight="1" s="49">
-      <c r="B78" s="172" t="inlineStr">
+      <c r="B78" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C78" s="168" t="inlineStr">
+      <c r="C78" s="169" t="inlineStr">
         <is>
           <t>Review Id hasSkinTone Skin Tone</t>
         </is>
       </c>
-      <c r="D78" s="173" t="inlineStr"/>
+      <c r="D78" s="174" t="inlineStr"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="49">
-      <c r="B79" s="172" t="inlineStr">
+      <c r="B79" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C79" s="168" t="inlineStr">
+      <c r="C79" s="169" t="inlineStr">
         <is>
           <t>Review Id aboutProduct Product</t>
         </is>
       </c>
-      <c r="D79" s="173" t="inlineStr"/>
+      <c r="D79" s="174" t="inlineStr"/>
     </row>
     <row r="80" ht="32" customHeight="1" s="49">
-      <c r="B80" s="172" t="inlineStr">
+      <c r="B80" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C80" s="168" t="inlineStr">
+      <c r="C80" s="169" t="inlineStr">
         <is>
           <t>Product hasCategory Category</t>
         </is>
       </c>
-      <c r="D80" s="173" t="inlineStr">
+      <c r="D80" s="174" t="inlineStr">
         <is>
           <t>They admit this one was never implemented. They used rdf:type instead and found out too late.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="49">
-      <c r="B81" s="172" t="inlineStr">
+      <c r="B81" s="173" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="C81" s="168" t="inlineStr">
+      <c r="C81" s="169" t="inlineStr">
         <is>
           <t>Product hasReviewId Review Id</t>
         </is>
       </c>
-      <c r="D81" s="173" t="inlineStr"/>
+      <c r="D81" s="174" t="inlineStr"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="49">
-      <c r="B82" s="172" t="inlineStr">
+      <c r="B82" s="173" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C82" s="168" t="inlineStr">
+      <c r="C82" s="169" t="inlineStr">
         <is>
           <t>Product hasRating</t>
         </is>
       </c>
-      <c r="D82" s="173" t="inlineStr"/>
+      <c r="D82" s="174" t="inlineStr"/>
     </row>
     <row r="83" ht="19" customHeight="1" s="49">
-      <c r="B83" s="172" t="inlineStr">
+      <c r="B83" s="173" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C83" s="168" t="inlineStr">
+      <c r="C83" s="169" t="inlineStr">
         <is>
           <t>Product hasOilyScore</t>
         </is>
       </c>
-      <c r="D83" s="173" t="inlineStr">
+      <c r="D83" s="174" t="inlineStr">
         <is>
           <t>and hasDryScore, hasNormalScore, hasCombinationScore</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="49">
-      <c r="B84" s="172" t="inlineStr">
+      <c r="B84" s="173" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C84" s="168" t="inlineStr">
+      <c r="C84" s="169" t="inlineStr">
         <is>
           <t>Country hasSephoraWebPage</t>
         </is>
       </c>
-      <c r="D84" s="173" t="inlineStr"/>
+      <c r="D84" s="174" t="inlineStr"/>
     </row>
     <row r="86" ht="24" customHeight="1" s="49">
-      <c r="A86" s="154" t="inlineStr">
+      <c r="A86" s="157" t="inlineStr">
         <is>
           <t>6. What is wrong with it. Say these first.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1" s="49">
-      <c r="B87" s="162" t="inlineStr">
+      <c r="B87" s="163" t="inlineStr">
         <is>
           <t>They say it themselves</t>
         </is>
       </c>
-      <c r="C87" s="161" t="inlineStr">
+      <c r="C87" s="162" t="inlineStr">
         <is>
           <t>'The team found out about the mistake too late to modify it in the OntoRefine.' Product hasCategory Category was never implemented.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1" s="49">
-      <c r="B88" s="162" t="inlineStr">
+      <c r="B88" s="163" t="inlineStr">
         <is>
           <t>They say it themselves</t>
         </is>
       </c>
-      <c r="C88" s="161" t="inlineStr">
+      <c r="C88" s="162" t="inlineStr">
         <is>
           <t>'The team was under time-pressure hence the output shows a whole URI instead of only a product.' The interface prints raw IRIs.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1" s="49">
-      <c r="B89" s="162" t="inlineStr">
+      <c r="B89" s="163" t="inlineStr">
         <is>
           <t>No evaluation</t>
         </is>
       </c>
-      <c r="C89" s="161" t="inlineStr">
+      <c r="C89" s="162" t="inlineStr">
         <is>
           <t>One worked example for one made-up user. No precision, no recall, no user study, no competency questions.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1" s="49">
-      <c r="B90" s="162" t="inlineStr">
+      <c r="B90" s="163" t="inlineStr">
         <is>
           <t>Nothing published</t>
         </is>
       </c>
-      <c r="C90" s="161" t="inlineStr">
+      <c r="C90" s="162" t="inlineStr">
         <is>
           <t>No OWL file, no permanent address, no DOI. I cannot download it and neither can anyone else.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1" s="49">
-      <c r="B91" s="162" t="inlineStr">
+      <c r="B91" s="163" t="inlineStr">
         <is>
           <t>The deeper problem</t>
         </is>
       </c>
-      <c r="C91" s="161" t="inlineStr">
+      <c r="C91" s="162" t="inlineStr">
         <is>
           <t>The recommendation comes from star ratings only. The system never looks at what is inside the product. Two products with a 5 are identical to it, even if one is full of fragrance allergens and the other is not.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" s="49">
-      <c r="A93" s="154" t="inlineStr">
+      <c r="A93" s="157" t="inlineStr">
         <is>
           <t>7. Their third limitation</t>
         </is>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1" s="49">
-      <c r="B94" s="167" t="inlineStr">
+      <c r="B94" s="168" t="inlineStr">
         <is>
           <t>In their own words:
    "Lastly, class restrictions based on ingredients could be developed.
